--- a/data/entrada/inventario/servicios.xlsx
+++ b/data/entrada/inventario/servicios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amarzal/_Activo/CoAna/data/entrada/superficies/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amarzal/_Activo/eco/CoAna/data/entrada/inventario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D190BCE8-E399-0E4B-9FB6-D153D2ADDB0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E514A12B-A438-1040-BA70-8A68ED555197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="600" windowWidth="33880" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="660" windowWidth="33880" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -142,9 +142,6 @@
     <t>Oficina de Cooperació en Investigació i Desenvolupament Tecnològic</t>
   </si>
   <si>
-    <t>ocit</t>
-  </si>
-  <si>
     <t>Registre General</t>
   </si>
   <si>
@@ -3263,6 +3260,9 @@
   </si>
   <si>
     <t>asesoría-jurídica</t>
+  </si>
+  <si>
+    <t>sgit</t>
   </si>
 </sst>
 </file>
@@ -3903,7 +3903,7 @@
         <v>1</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -3917,7 +3917,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>40</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -3925,13 +3925,13 @@
         <v>248</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C21" s="1">
         <v>1</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -3939,13 +3939,13 @@
         <v>251</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C22" s="1">
         <v>1</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -3953,13 +3953,13 @@
         <v>261</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" s="1">
         <v>1</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -3967,13 +3967,13 @@
         <v>263</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C24" s="1">
         <v>1</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -3981,13 +3981,13 @@
         <v>264</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C25" s="1">
         <v>1</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
@@ -3995,13 +3995,13 @@
         <v>311</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C26" s="1">
         <v>1</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -4009,13 +4009,13 @@
         <v>350</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C27" s="1">
         <v>1</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
@@ -4023,13 +4023,13 @@
         <v>361</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C28" s="1">
         <v>1</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
@@ -4037,13 +4037,13 @@
         <v>362</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C29" s="1">
         <v>1</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
@@ -4051,13 +4051,13 @@
         <v>364</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C30" s="1">
         <v>1</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
@@ -4065,13 +4065,13 @@
         <v>366</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C31" s="1">
         <v>1</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
@@ -4079,13 +4079,13 @@
         <v>372</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C32" s="1">
         <v>1</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
@@ -4093,13 +4093,13 @@
         <v>374</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C33" s="1">
         <v>1</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
@@ -4107,13 +4107,13 @@
         <v>377</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C34" s="1">
         <v>1</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
@@ -4121,13 +4121,13 @@
         <v>378</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C35" s="1">
         <v>1</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
@@ -4135,13 +4135,13 @@
         <v>440</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C36" s="1">
         <v>1</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
@@ -4149,13 +4149,13 @@
         <v>480</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C37" s="1">
         <v>1</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
@@ -4163,13 +4163,13 @@
         <v>522</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C38" s="1">
         <v>1</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
@@ -4177,13 +4177,13 @@
         <v>523</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C39" s="1">
         <v>1</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
@@ -4191,13 +4191,13 @@
         <v>620</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C40" s="1">
         <v>1</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
@@ -4205,13 +4205,13 @@
         <v>640</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C41" s="1">
         <v>1</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
@@ -4219,13 +4219,13 @@
         <v>660</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C42" s="1">
         <v>1</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
@@ -4233,13 +4233,13 @@
         <v>720</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C43" s="1">
         <v>1</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
@@ -4247,13 +4247,13 @@
         <v>760</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C44" s="1">
         <v>1</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
@@ -4261,13 +4261,13 @@
         <v>1442</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C45" s="1">
         <v>1</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
@@ -4275,13 +4275,13 @@
         <v>1443</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C46" s="1">
         <v>1</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
@@ -4289,13 +4289,13 @@
         <v>1529</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C47" s="1">
         <v>1</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
@@ -4303,13 +4303,13 @@
         <v>1530</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C48" s="1">
         <v>1</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
@@ -4317,13 +4317,13 @@
         <v>1543</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C49" s="1">
         <v>1</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
@@ -4331,13 +4331,13 @@
         <v>1544</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C50" s="1">
         <v>1</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
@@ -4345,13 +4345,13 @@
         <v>1602</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C51" s="1">
         <v>1</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
@@ -4359,13 +4359,13 @@
         <v>1662</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C52" s="1">
         <v>1</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
@@ -4373,13 +4373,13 @@
         <v>1702</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C53" s="1">
         <v>1</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
@@ -4387,13 +4387,13 @@
         <v>1722</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C54" s="1">
         <v>1</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
@@ -4401,13 +4401,13 @@
         <v>1723</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C55" s="1">
         <v>1</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
@@ -4415,13 +4415,13 @@
         <v>1862</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C56" s="1">
         <v>1</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
@@ -4429,13 +4429,13 @@
         <v>1882</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C57" s="1">
         <v>1</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
@@ -4443,13 +4443,13 @@
         <v>1883</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C58" s="1">
         <v>1</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
@@ -4457,13 +4457,13 @@
         <v>1902</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C59" s="1">
         <v>1</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
@@ -4471,13 +4471,13 @@
         <v>1982</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C60" s="1">
         <v>1</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
@@ -4485,13 +4485,13 @@
         <v>2022</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C61" s="1">
         <v>1</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
@@ -4499,13 +4499,13 @@
         <v>2102</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C62" s="1">
         <v>1</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
@@ -4513,13 +4513,13 @@
         <v>2103</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C63" s="1">
         <v>1</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
@@ -4527,13 +4527,13 @@
         <v>2142</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C64" s="1">
         <v>1</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
@@ -4541,13 +4541,13 @@
         <v>2162</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C65" s="1">
         <v>1</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
@@ -4555,13 +4555,13 @@
         <v>2182</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C66" s="1">
         <v>1</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
@@ -4569,13 +4569,13 @@
         <v>2183</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C67" s="1">
         <v>1</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
@@ -4583,13 +4583,13 @@
         <v>2202</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C68" s="1">
         <v>1</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
@@ -4597,13 +4597,13 @@
         <v>2224</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C69" s="1">
         <v>1</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
@@ -4611,13 +4611,13 @@
         <v>2283</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C70" s="1">
         <v>1</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
@@ -4625,13 +4625,13 @@
         <v>2284</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C71" s="1">
         <v>1</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
@@ -4639,13 +4639,13 @@
         <v>2322</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C72" s="1">
         <v>1</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
@@ -4653,13 +4653,13 @@
         <v>2342</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C73" s="1">
         <v>1</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
@@ -4667,13 +4667,13 @@
         <v>2382</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C74" s="1">
         <v>1</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
@@ -4681,13 +4681,13 @@
         <v>2422</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C75" s="1">
         <v>1</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
@@ -4695,13 +4695,13 @@
         <v>2502</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C76" s="1">
         <v>1</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
@@ -4709,13 +4709,13 @@
         <v>2503</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C77" s="1">
         <v>1</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
@@ -4723,13 +4723,13 @@
         <v>2562</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C78" s="1">
         <v>1</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
@@ -4737,13 +4737,13 @@
         <v>2603</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C79" s="1">
         <v>1</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
@@ -4751,13 +4751,13 @@
         <v>2604</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C80" s="1">
         <v>1</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
@@ -4765,13 +4765,13 @@
         <v>2662</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C81" s="1">
         <v>1</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
@@ -4779,13 +4779,13 @@
         <v>2722</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C82" s="1">
         <v>1</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
@@ -4793,13 +4793,13 @@
         <v>2822</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C83" s="1">
         <v>1</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
@@ -4807,13 +4807,13 @@
         <v>2882</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C84" s="1">
         <v>1</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
@@ -4821,13 +4821,13 @@
         <v>2883</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C85" s="1">
         <v>1</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
@@ -4835,13 +4835,13 @@
         <v>2922</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C86" s="1">
         <v>1</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
@@ -4849,13 +4849,13 @@
         <v>2942</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C87" s="1">
         <v>1</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
@@ -4863,13 +4863,13 @@
         <v>2943</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C88" s="1">
         <v>1</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
@@ -4877,13 +4877,13 @@
         <v>2984</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C89" s="1">
         <v>1</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
@@ -4891,13 +4891,13 @@
         <v>3004</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C90" s="1">
         <v>1</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
@@ -4905,13 +4905,13 @@
         <v>3103</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C91" s="1">
         <v>1</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
@@ -4919,13 +4919,13 @@
         <v>3145</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C92" s="1">
         <v>1</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
@@ -4933,13 +4933,13 @@
         <v>3165</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C93" s="1">
         <v>1</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
@@ -4947,13 +4947,13 @@
         <v>3285</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C94" s="1">
         <v>1</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
@@ -4961,7 +4961,7 @@
         <v>3405</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C95" s="1">
         <v>1</v>
@@ -4975,13 +4975,13 @@
         <v>3406</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C96" s="1">
         <v>1</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
@@ -4989,13 +4989,13 @@
         <v>3408</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C97" s="1">
         <v>1</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
@@ -5003,13 +5003,13 @@
         <v>3425</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C98" s="1">
         <v>1</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
@@ -5017,13 +5017,13 @@
         <v>3427</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C99" s="1">
         <v>1</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
@@ -5031,13 +5031,13 @@
         <v>3465</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C100" s="1">
         <v>1</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
@@ -5045,13 +5045,13 @@
         <v>3466</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C101" s="1">
         <v>1</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
@@ -5059,13 +5059,13 @@
         <v>3847</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C102" s="1">
         <v>1</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
@@ -5073,13 +5073,13 @@
         <v>3907</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C103" s="1">
         <v>1</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
@@ -5087,13 +5087,13 @@
         <v>3987</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C104" s="1">
         <v>1</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
@@ -5101,13 +5101,13 @@
         <v>4027</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C105" s="1">
         <v>1</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
@@ -5115,13 +5115,13 @@
         <v>4107</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C106" s="1">
         <v>1</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
@@ -5129,13 +5129,13 @@
         <v>4147</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C107" s="1">
         <v>1</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
@@ -5143,13 +5143,13 @@
         <v>4167</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C108" s="1">
         <v>1</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
@@ -5157,13 +5157,13 @@
         <v>4168</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C109" s="1">
         <v>1</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
@@ -5171,13 +5171,13 @@
         <v>4207</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C110" s="1">
         <v>1</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
@@ -5185,13 +5185,13 @@
         <v>4247</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C111" s="1">
         <v>1</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
@@ -5199,13 +5199,13 @@
         <v>4248</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C112" s="1">
         <v>1</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
@@ -5213,13 +5213,13 @@
         <v>4249</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C113" s="1">
         <v>1</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
@@ -5227,13 +5227,13 @@
         <v>4250</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C114" s="1">
         <v>1</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.2">
@@ -5241,13 +5241,13 @@
         <v>4251</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C115" s="1">
         <v>1</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.2">
@@ -5255,13 +5255,13 @@
         <v>4252</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C116" s="1">
         <v>1</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
@@ -5269,13 +5269,13 @@
         <v>4253</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C117" s="1">
         <v>1</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
@@ -5283,13 +5283,13 @@
         <v>4254</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C118" s="1">
         <v>1</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.2">
@@ -5297,13 +5297,13 @@
         <v>4255</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C119" s="1">
         <v>1</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.2">
@@ -5311,7 +5311,7 @@
         <v>4427</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C120" s="1">
         <v>1</v>
@@ -5325,13 +5325,13 @@
         <v>4487</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C121" s="1">
         <v>1</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
@@ -5339,13 +5339,13 @@
         <v>4488</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C122" s="1">
         <v>1</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.2">
@@ -5353,13 +5353,13 @@
         <v>4489</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C123" s="1">
         <v>1</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.2">
@@ -5367,13 +5367,13 @@
         <v>4567</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C124" s="1">
         <v>1</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.2">
@@ -5381,13 +5381,13 @@
         <v>4607</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C125" s="1">
         <v>1</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.2">
@@ -5395,13 +5395,13 @@
         <v>4647</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C126" s="1">
         <v>1</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.2">
@@ -5409,13 +5409,13 @@
         <v>4791</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C127" s="1">
         <v>1</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.2">
@@ -5423,7 +5423,7 @@
         <v>4907</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C128" s="1">
         <v>1</v>
@@ -5437,13 +5437,13 @@
         <v>4987</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C129" s="1">
         <v>1</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.2">
@@ -5451,7 +5451,7 @@
         <v>1</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C130" s="1">
         <v>0</v>
@@ -5463,7 +5463,7 @@
         <v>5</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C131" s="1">
         <v>0</v>
@@ -5475,7 +5475,7 @@
         <v>82</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C132" s="1">
         <v>0</v>
@@ -5487,7 +5487,7 @@
         <v>83</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C133" s="1">
         <v>0</v>
@@ -5499,7 +5499,7 @@
         <v>84</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C134" s="1">
         <v>0</v>
@@ -5511,7 +5511,7 @@
         <v>85</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C135" s="1">
         <v>0</v>
@@ -5523,7 +5523,7 @@
         <v>86</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C136" s="1">
         <v>0</v>
@@ -5535,7 +5535,7 @@
         <v>87</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C137" s="1">
         <v>0</v>
@@ -5547,7 +5547,7 @@
         <v>88</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C138" s="1">
         <v>0</v>
@@ -5559,7 +5559,7 @@
         <v>91</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C139" s="1">
         <v>0</v>
@@ -5571,7 +5571,7 @@
         <v>94</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C140" s="1">
         <v>0</v>
@@ -5583,7 +5583,7 @@
         <v>100</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C141" s="1">
         <v>0</v>
@@ -5595,7 +5595,7 @@
         <v>103</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C142" s="1">
         <v>0</v>
@@ -5607,7 +5607,7 @@
         <v>105</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C143" s="1">
         <v>0</v>
@@ -5619,7 +5619,7 @@
         <v>106</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C144" s="1">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>107</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C145" s="1">
         <v>0</v>
@@ -5643,7 +5643,7 @@
         <v>108</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C146" s="1">
         <v>0</v>
@@ -5655,7 +5655,7 @@
         <v>109</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C147" s="1">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>110</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C148" s="1">
         <v>0</v>
@@ -5679,7 +5679,7 @@
         <v>111</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C149" s="1">
         <v>0</v>
@@ -5691,7 +5691,7 @@
         <v>112</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C150" s="1">
         <v>0</v>
@@ -5703,7 +5703,7 @@
         <v>113</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C151" s="1">
         <v>0</v>
@@ -5715,7 +5715,7 @@
         <v>114</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C152" s="1">
         <v>0</v>
@@ -5727,7 +5727,7 @@
         <v>115</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C153" s="1">
         <v>0</v>
@@ -5739,7 +5739,7 @@
         <v>116</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C154" s="1">
         <v>0</v>
@@ -5751,7 +5751,7 @@
         <v>117</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C155" s="1">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>118</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C156" s="1">
         <v>0</v>
@@ -5775,7 +5775,7 @@
         <v>119</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C157" s="1">
         <v>0</v>
@@ -5787,7 +5787,7 @@
         <v>120</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C158" s="1">
         <v>0</v>
@@ -5799,7 +5799,7 @@
         <v>121</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C159" s="1">
         <v>0</v>
@@ -5811,7 +5811,7 @@
         <v>122</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C160" s="1">
         <v>0</v>
@@ -5823,7 +5823,7 @@
         <v>123</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C161" s="1">
         <v>0</v>
@@ -5835,7 +5835,7 @@
         <v>124</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C162" s="1">
         <v>0</v>
@@ -5847,7 +5847,7 @@
         <v>125</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C163" s="1">
         <v>0</v>
@@ -5859,7 +5859,7 @@
         <v>126</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C164" s="1">
         <v>0</v>
@@ -5871,7 +5871,7 @@
         <v>127</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C165" s="1">
         <v>0</v>
@@ -5883,7 +5883,7 @@
         <v>128</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C166" s="1">
         <v>0</v>
@@ -5895,7 +5895,7 @@
         <v>129</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C167" s="1">
         <v>0</v>
@@ -5907,7 +5907,7 @@
         <v>130</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C168" s="1">
         <v>0</v>
@@ -5919,7 +5919,7 @@
         <v>131</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C169" s="1">
         <v>0</v>
@@ -5931,7 +5931,7 @@
         <v>132</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C170" s="1">
         <v>0</v>
@@ -5943,7 +5943,7 @@
         <v>133</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C171" s="1">
         <v>0</v>
@@ -5955,7 +5955,7 @@
         <v>134</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C172" s="1">
         <v>0</v>
@@ -5967,7 +5967,7 @@
         <v>135</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C173" s="1">
         <v>0</v>
@@ -5979,7 +5979,7 @@
         <v>136</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C174" s="1">
         <v>0</v>
@@ -5991,7 +5991,7 @@
         <v>137</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C175" s="1">
         <v>0</v>
@@ -6003,7 +6003,7 @@
         <v>139</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C176" s="1">
         <v>0</v>
@@ -6015,7 +6015,7 @@
         <v>140</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C177" s="1">
         <v>0</v>
@@ -6027,7 +6027,7 @@
         <v>141</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C178" s="1">
         <v>0</v>
@@ -6039,7 +6039,7 @@
         <v>142</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C179" s="1">
         <v>0</v>
@@ -6051,7 +6051,7 @@
         <v>143</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C180" s="1">
         <v>0</v>
@@ -6063,7 +6063,7 @@
         <v>144</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C181" s="1">
         <v>0</v>
@@ -6075,7 +6075,7 @@
         <v>145</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C182" s="1">
         <v>0</v>
@@ -6087,7 +6087,7 @@
         <v>146</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C183" s="1">
         <v>0</v>
@@ -6099,7 +6099,7 @@
         <v>147</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C184" s="1">
         <v>0</v>
@@ -6111,7 +6111,7 @@
         <v>148</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C185" s="1">
         <v>0</v>
@@ -6123,7 +6123,7 @@
         <v>149</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C186" s="1">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>150</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C187" s="1">
         <v>0</v>
@@ -6147,7 +6147,7 @@
         <v>151</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C188" s="1">
         <v>0</v>
@@ -6159,7 +6159,7 @@
         <v>152</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C189" s="1">
         <v>0</v>
@@ -6171,7 +6171,7 @@
         <v>153</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C190" s="1">
         <v>0</v>
@@ -6183,7 +6183,7 @@
         <v>154</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C191" s="1">
         <v>0</v>
@@ -6195,7 +6195,7 @@
         <v>155</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C192" s="1">
         <v>0</v>
@@ -6207,7 +6207,7 @@
         <v>156</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C193" s="1">
         <v>0</v>
@@ -6219,7 +6219,7 @@
         <v>157</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C194" s="1">
         <v>0</v>
@@ -6231,7 +6231,7 @@
         <v>158</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C195" s="1">
         <v>0</v>
@@ -6243,7 +6243,7 @@
         <v>159</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C196" s="1">
         <v>0</v>
@@ -6255,7 +6255,7 @@
         <v>160</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C197" s="1">
         <v>0</v>
@@ -6267,7 +6267,7 @@
         <v>161</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C198" s="1">
         <v>0</v>
@@ -6279,7 +6279,7 @@
         <v>162</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C199" s="1">
         <v>0</v>
@@ -6291,7 +6291,7 @@
         <v>163</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C200" s="1">
         <v>0</v>
@@ -6303,7 +6303,7 @@
         <v>164</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C201" s="1">
         <v>0</v>
@@ -6315,7 +6315,7 @@
         <v>165</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C202" s="1">
         <v>0</v>
@@ -6327,7 +6327,7 @@
         <v>166</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C203" s="1">
         <v>0</v>
@@ -6339,7 +6339,7 @@
         <v>167</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C204" s="1">
         <v>0</v>
@@ -6351,7 +6351,7 @@
         <v>168</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C205" s="1">
         <v>0</v>
@@ -6363,7 +6363,7 @@
         <v>169</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C206" s="1">
         <v>0</v>
@@ -6375,7 +6375,7 @@
         <v>170</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C207" s="1">
         <v>0</v>
@@ -6387,7 +6387,7 @@
         <v>171</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C208" s="1">
         <v>0</v>
@@ -6399,7 +6399,7 @@
         <v>172</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C209" s="1">
         <v>0</v>
@@ -6411,7 +6411,7 @@
         <v>173</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C210" s="1">
         <v>0</v>
@@ -6423,7 +6423,7 @@
         <v>174</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C211" s="1">
         <v>0</v>
@@ -6435,7 +6435,7 @@
         <v>175</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C212" s="1">
         <v>0</v>
@@ -6447,7 +6447,7 @@
         <v>176</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C213" s="1">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>178</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C214" s="1">
         <v>0</v>
@@ -6471,7 +6471,7 @@
         <v>179</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C215" s="1">
         <v>0</v>
@@ -6483,7 +6483,7 @@
         <v>180</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C216" s="1">
         <v>0</v>
@@ -6495,7 +6495,7 @@
         <v>181</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C217" s="1">
         <v>0</v>
@@ -6507,7 +6507,7 @@
         <v>182</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C218" s="1">
         <v>0</v>
@@ -6519,7 +6519,7 @@
         <v>183</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C219" s="1">
         <v>0</v>
@@ -6531,7 +6531,7 @@
         <v>184</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C220" s="1">
         <v>0</v>
@@ -6543,7 +6543,7 @@
         <v>185</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C221" s="1">
         <v>0</v>
@@ -6555,7 +6555,7 @@
         <v>186</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C222" s="1">
         <v>0</v>
@@ -6567,7 +6567,7 @@
         <v>187</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C223" s="1">
         <v>0</v>
@@ -6579,7 +6579,7 @@
         <v>188</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C224" s="1">
         <v>0</v>
@@ -6591,7 +6591,7 @@
         <v>189</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C225" s="1">
         <v>0</v>
@@ -6603,7 +6603,7 @@
         <v>190</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C226" s="1">
         <v>0</v>
@@ -6615,7 +6615,7 @@
         <v>191</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C227" s="1">
         <v>0</v>
@@ -6627,7 +6627,7 @@
         <v>192</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C228" s="1">
         <v>0</v>
@@ -6639,7 +6639,7 @@
         <v>193</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C229" s="1">
         <v>0</v>
@@ -6651,7 +6651,7 @@
         <v>194</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C230" s="1">
         <v>0</v>
@@ -6663,7 +6663,7 @@
         <v>195</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C231" s="1">
         <v>0</v>
@@ -6675,7 +6675,7 @@
         <v>196</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C232" s="1">
         <v>0</v>
@@ -6687,7 +6687,7 @@
         <v>197</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C233" s="1">
         <v>0</v>
@@ -6699,7 +6699,7 @@
         <v>198</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C234" s="1">
         <v>0</v>
@@ -6711,7 +6711,7 @@
         <v>199</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C235" s="1">
         <v>0</v>
@@ -6723,7 +6723,7 @@
         <v>200</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C236" s="1">
         <v>0</v>
@@ -6735,7 +6735,7 @@
         <v>201</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C237" s="1">
         <v>0</v>
@@ -6747,7 +6747,7 @@
         <v>202</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C238" s="1">
         <v>0</v>
@@ -6759,7 +6759,7 @@
         <v>203</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C239" s="1">
         <v>0</v>
@@ -6771,7 +6771,7 @@
         <v>204</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C240" s="1">
         <v>0</v>
@@ -6783,7 +6783,7 @@
         <v>205</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C241" s="1">
         <v>0</v>
@@ -6795,7 +6795,7 @@
         <v>206</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C242" s="1">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>207</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C243" s="1">
         <v>0</v>
@@ -6819,7 +6819,7 @@
         <v>208</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C244" s="1">
         <v>0</v>
@@ -6831,7 +6831,7 @@
         <v>209</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C245" s="1">
         <v>0</v>
@@ -6843,7 +6843,7 @@
         <v>210</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C246" s="1">
         <v>0</v>
@@ -6855,7 +6855,7 @@
         <v>211</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C247" s="1">
         <v>0</v>
@@ -6867,7 +6867,7 @@
         <v>213</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C248" s="1">
         <v>0</v>
@@ -6879,7 +6879,7 @@
         <v>214</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C249" s="1">
         <v>0</v>
@@ -6891,7 +6891,7 @@
         <v>215</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C250" s="1">
         <v>0</v>
@@ -6903,7 +6903,7 @@
         <v>216</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C251" s="1">
         <v>0</v>
@@ -6915,7 +6915,7 @@
         <v>217</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C252" s="1">
         <v>0</v>
@@ -6927,7 +6927,7 @@
         <v>219</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C253" s="1">
         <v>0</v>
@@ -6939,7 +6939,7 @@
         <v>221</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C254" s="1">
         <v>0</v>
@@ -6951,7 +6951,7 @@
         <v>227</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C255" s="1">
         <v>0</v>
@@ -6963,7 +6963,7 @@
         <v>228</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C256" s="1">
         <v>0</v>
@@ -6975,7 +6975,7 @@
         <v>229</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C257" s="1">
         <v>0</v>
@@ -6987,7 +6987,7 @@
         <v>230</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C258" s="1">
         <v>0</v>
@@ -6999,7 +6999,7 @@
         <v>231</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C259" s="1">
         <v>0</v>
@@ -7011,7 +7011,7 @@
         <v>232</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C260" s="1">
         <v>0</v>
@@ -7023,7 +7023,7 @@
         <v>233</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C261" s="1">
         <v>0</v>
@@ -7035,7 +7035,7 @@
         <v>234</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C262" s="1">
         <v>0</v>
@@ -7047,7 +7047,7 @@
         <v>235</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C263" s="1">
         <v>0</v>
@@ -7059,7 +7059,7 @@
         <v>236</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C264" s="1">
         <v>0</v>
@@ -7071,7 +7071,7 @@
         <v>238</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C265" s="1">
         <v>0</v>
@@ -7083,7 +7083,7 @@
         <v>239</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C266" s="1">
         <v>0</v>
@@ -7095,7 +7095,7 @@
         <v>240</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C267" s="1">
         <v>0</v>
@@ -7107,7 +7107,7 @@
         <v>241</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C268" s="1">
         <v>0</v>
@@ -7119,7 +7119,7 @@
         <v>243</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C269" s="1">
         <v>0</v>
@@ -7131,7 +7131,7 @@
         <v>244</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C270" s="1">
         <v>0</v>
@@ -7143,7 +7143,7 @@
         <v>245</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C271" s="1">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>246</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C272" s="1">
         <v>0</v>
@@ -7167,7 +7167,7 @@
         <v>247</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C273" s="1">
         <v>0</v>
@@ -7179,7 +7179,7 @@
         <v>249</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C274" s="1">
         <v>0</v>
@@ -7191,7 +7191,7 @@
         <v>250</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C275" s="1">
         <v>0</v>
@@ -7203,7 +7203,7 @@
         <v>252</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C276" s="1">
         <v>0</v>
@@ -7215,7 +7215,7 @@
         <v>253</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C277" s="1">
         <v>0</v>
@@ -7227,7 +7227,7 @@
         <v>254</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C278" s="1">
         <v>0</v>
@@ -7239,7 +7239,7 @@
         <v>255</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C279" s="1">
         <v>0</v>
@@ -7251,7 +7251,7 @@
         <v>256</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C280" s="1">
         <v>0</v>
@@ -7263,7 +7263,7 @@
         <v>257</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C281" s="1">
         <v>0</v>
@@ -7275,7 +7275,7 @@
         <v>258</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C282" s="1">
         <v>0</v>
@@ -7287,7 +7287,7 @@
         <v>259</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C283" s="1">
         <v>0</v>
@@ -7299,7 +7299,7 @@
         <v>260</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C284" s="1">
         <v>0</v>
@@ -7311,7 +7311,7 @@
         <v>265</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C285" s="1">
         <v>0</v>
@@ -7323,7 +7323,7 @@
         <v>266</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C286" s="1">
         <v>0</v>
@@ -7335,7 +7335,7 @@
         <v>267</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C287" s="1">
         <v>0</v>
@@ -7347,7 +7347,7 @@
         <v>268</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C288" s="1">
         <v>0</v>
@@ -7359,7 +7359,7 @@
         <v>269</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C289" s="1">
         <v>0</v>
@@ -7371,7 +7371,7 @@
         <v>270</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C290" s="1">
         <v>0</v>
@@ -7383,7 +7383,7 @@
         <v>271</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C291" s="1">
         <v>0</v>
@@ -7395,7 +7395,7 @@
         <v>272</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C292" s="1">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         <v>273</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C293" s="1">
         <v>0</v>
@@ -7419,7 +7419,7 @@
         <v>274</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C294" s="1">
         <v>0</v>
@@ -7431,7 +7431,7 @@
         <v>275</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C295" s="1">
         <v>0</v>
@@ -7443,7 +7443,7 @@
         <v>279</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C296" s="1">
         <v>0</v>
@@ -7455,7 +7455,7 @@
         <v>280</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C297" s="1">
         <v>0</v>
@@ -7467,7 +7467,7 @@
         <v>281</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C298" s="1">
         <v>0</v>
@@ -7479,7 +7479,7 @@
         <v>282</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C299" s="1">
         <v>0</v>
@@ -7491,7 +7491,7 @@
         <v>284</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C300" s="1">
         <v>0</v>
@@ -7503,7 +7503,7 @@
         <v>285</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C301" s="1">
         <v>0</v>
@@ -7515,7 +7515,7 @@
         <v>286</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C302" s="1">
         <v>0</v>
@@ -7527,7 +7527,7 @@
         <v>287</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C303" s="1">
         <v>0</v>
@@ -7539,7 +7539,7 @@
         <v>288</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C304" s="1">
         <v>0</v>
@@ -7551,7 +7551,7 @@
         <v>289</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C305" s="1">
         <v>0</v>
@@ -7563,7 +7563,7 @@
         <v>290</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C306" s="1">
         <v>0</v>
@@ -7575,7 +7575,7 @@
         <v>291</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C307" s="1">
         <v>0</v>
@@ -7587,7 +7587,7 @@
         <v>292</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C308" s="1">
         <v>0</v>
@@ -7599,7 +7599,7 @@
         <v>293</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C309" s="1">
         <v>0</v>
@@ -7611,7 +7611,7 @@
         <v>294</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C310" s="1">
         <v>0</v>
@@ -7623,7 +7623,7 @@
         <v>295</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C311" s="1">
         <v>0</v>
@@ -7635,7 +7635,7 @@
         <v>296</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C312" s="1">
         <v>0</v>
@@ -7647,7 +7647,7 @@
         <v>297</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C313" s="1">
         <v>0</v>
@@ -7659,7 +7659,7 @@
         <v>298</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C314" s="1">
         <v>0</v>
@@ -7671,7 +7671,7 @@
         <v>299</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C315" s="1">
         <v>0</v>
@@ -7683,7 +7683,7 @@
         <v>300</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C316" s="1">
         <v>0</v>
@@ -7695,7 +7695,7 @@
         <v>301</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C317" s="1">
         <v>0</v>
@@ -7707,7 +7707,7 @@
         <v>302</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C318" s="1">
         <v>0</v>
@@ -7719,7 +7719,7 @@
         <v>303</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C319" s="1">
         <v>0</v>
@@ -7731,7 +7731,7 @@
         <v>304</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C320" s="1">
         <v>0</v>
@@ -7743,7 +7743,7 @@
         <v>305</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C321" s="1">
         <v>0</v>
@@ -7755,7 +7755,7 @@
         <v>306</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C322" s="1">
         <v>0</v>
@@ -7767,7 +7767,7 @@
         <v>307</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C323" s="1">
         <v>0</v>
@@ -7791,7 +7791,7 @@
         <v>309</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C325" s="1">
         <v>0</v>
@@ -7803,7 +7803,7 @@
         <v>310</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C326" s="1">
         <v>0</v>
@@ -7815,7 +7815,7 @@
         <v>312</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C327" s="1">
         <v>0</v>
@@ -7827,7 +7827,7 @@
         <v>313</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C328" s="1">
         <v>0</v>
@@ -7839,7 +7839,7 @@
         <v>314</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C329" s="1">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>315</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C330" s="1">
         <v>0</v>
@@ -7863,7 +7863,7 @@
         <v>316</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C331" s="1">
         <v>0</v>
@@ -7875,7 +7875,7 @@
         <v>317</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C332" s="1">
         <v>0</v>
@@ -7887,7 +7887,7 @@
         <v>318</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C333" s="1">
         <v>0</v>
@@ -7899,7 +7899,7 @@
         <v>319</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C334" s="1">
         <v>0</v>
@@ -7911,7 +7911,7 @@
         <v>320</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C335" s="1">
         <v>0</v>
@@ -7923,7 +7923,7 @@
         <v>321</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C336" s="1">
         <v>0</v>
@@ -7935,7 +7935,7 @@
         <v>322</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C337" s="1">
         <v>0</v>
@@ -7947,7 +7947,7 @@
         <v>323</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C338" s="1">
         <v>0</v>
@@ -7959,7 +7959,7 @@
         <v>324</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C339" s="1">
         <v>0</v>
@@ -7971,7 +7971,7 @@
         <v>326</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C340" s="1">
         <v>0</v>
@@ -7983,7 +7983,7 @@
         <v>330</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C341" s="1">
         <v>0</v>
@@ -7995,7 +7995,7 @@
         <v>331</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C342" s="1">
         <v>0</v>
@@ -8007,7 +8007,7 @@
         <v>332</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C343" s="1">
         <v>0</v>
@@ -8019,7 +8019,7 @@
         <v>333</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C344" s="1">
         <v>0</v>
@@ -8031,7 +8031,7 @@
         <v>334</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C345" s="1">
         <v>0</v>
@@ -8043,7 +8043,7 @@
         <v>335</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C346" s="1">
         <v>0</v>
@@ -8055,7 +8055,7 @@
         <v>336</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C347" s="1">
         <v>0</v>
@@ -8067,7 +8067,7 @@
         <v>337</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C348" s="1">
         <v>0</v>
@@ -8079,7 +8079,7 @@
         <v>338</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C349" s="1">
         <v>0</v>
@@ -8091,7 +8091,7 @@
         <v>339</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C350" s="1">
         <v>0</v>
@@ -8103,7 +8103,7 @@
         <v>341</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C351" s="1">
         <v>0</v>
@@ -8115,7 +8115,7 @@
         <v>342</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C352" s="1">
         <v>0</v>
@@ -8127,7 +8127,7 @@
         <v>343</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C353" s="1">
         <v>0</v>
@@ -8139,7 +8139,7 @@
         <v>344</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C354" s="1">
         <v>0</v>
@@ -8151,7 +8151,7 @@
         <v>345</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C355" s="1">
         <v>0</v>
@@ -8163,7 +8163,7 @@
         <v>346</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C356" s="1">
         <v>0</v>
@@ -8175,7 +8175,7 @@
         <v>347</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C357" s="1">
         <v>0</v>
@@ -8187,7 +8187,7 @@
         <v>348</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C358" s="1">
         <v>0</v>
@@ -8199,7 +8199,7 @@
         <v>349</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C359" s="1">
         <v>0</v>
@@ -8211,7 +8211,7 @@
         <v>355</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C360" s="1">
         <v>0</v>
@@ -8223,7 +8223,7 @@
         <v>357</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C361" s="1">
         <v>0</v>
@@ -8235,7 +8235,7 @@
         <v>358</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C362" s="1">
         <v>0</v>
@@ -8247,7 +8247,7 @@
         <v>359</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C363" s="1">
         <v>0</v>
@@ -8259,7 +8259,7 @@
         <v>360</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C364" s="1">
         <v>0</v>
@@ -8271,7 +8271,7 @@
         <v>363</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C365" s="1">
         <v>0</v>
@@ -8283,7 +8283,7 @@
         <v>365</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C366" s="1">
         <v>0</v>
@@ -8295,7 +8295,7 @@
         <v>367</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C367" s="1">
         <v>0</v>
@@ -8307,7 +8307,7 @@
         <v>368</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C368" s="1">
         <v>0</v>
@@ -8319,7 +8319,7 @@
         <v>370</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C369" s="1">
         <v>0</v>
@@ -8331,7 +8331,7 @@
         <v>371</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C370" s="1">
         <v>0</v>
@@ -8343,7 +8343,7 @@
         <v>373</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C371" s="1">
         <v>0</v>
@@ -8355,7 +8355,7 @@
         <v>375</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C372" s="1">
         <v>0</v>
@@ -8367,7 +8367,7 @@
         <v>376</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C373" s="1">
         <v>0</v>
@@ -8379,7 +8379,7 @@
         <v>379</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C374" s="1">
         <v>0</v>
@@ -8391,7 +8391,7 @@
         <v>380</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C375" s="1">
         <v>0</v>
@@ -8403,7 +8403,7 @@
         <v>381</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C376" s="1">
         <v>0</v>
@@ -8415,7 +8415,7 @@
         <v>382</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C377" s="1">
         <v>0</v>
@@ -8427,7 +8427,7 @@
         <v>383</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C378" s="1">
         <v>0</v>
@@ -8439,7 +8439,7 @@
         <v>384</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C379" s="1">
         <v>0</v>
@@ -8451,7 +8451,7 @@
         <v>385</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C380" s="1">
         <v>0</v>
@@ -8463,7 +8463,7 @@
         <v>386</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C381" s="1">
         <v>0</v>
@@ -8475,7 +8475,7 @@
         <v>387</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C382" s="1">
         <v>0</v>
@@ -8487,7 +8487,7 @@
         <v>388</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C383" s="1">
         <v>0</v>
@@ -8499,7 +8499,7 @@
         <v>389</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C384" s="1">
         <v>0</v>
@@ -8511,7 +8511,7 @@
         <v>390</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C385" s="1">
         <v>0</v>
@@ -8523,7 +8523,7 @@
         <v>481</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C386" s="1">
         <v>0</v>
@@ -8535,7 +8535,7 @@
         <v>482</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C387" s="1">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>520</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C388" s="1">
         <v>0</v>
@@ -8559,7 +8559,7 @@
         <v>521</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C389" s="1">
         <v>0</v>
@@ -8571,7 +8571,7 @@
         <v>540</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C390" s="1">
         <v>0</v>
@@ -8583,7 +8583,7 @@
         <v>560</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C391" s="1">
         <v>0</v>
@@ -8595,7 +8595,7 @@
         <v>580</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C392" s="1">
         <v>0</v>
@@ -8607,7 +8607,7 @@
         <v>600</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C393" s="1">
         <v>0</v>
@@ -8619,7 +8619,7 @@
         <v>601</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C394" s="1">
         <v>0</v>
@@ -8631,7 +8631,7 @@
         <v>602</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C395" s="1">
         <v>0</v>
@@ -8643,7 +8643,7 @@
         <v>603</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C396" s="1">
         <v>0</v>
@@ -8655,7 +8655,7 @@
         <v>680</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C397" s="1">
         <v>0</v>
@@ -8667,7 +8667,7 @@
         <v>700</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C398" s="1">
         <v>0</v>
@@ -8679,7 +8679,7 @@
         <v>721</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C399" s="1">
         <v>0</v>
@@ -8691,7 +8691,7 @@
         <v>880</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C400" s="1">
         <v>0</v>
@@ -8703,7 +8703,7 @@
         <v>980</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C401" s="1">
         <v>0</v>
@@ -8715,7 +8715,7 @@
         <v>1000</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C402" s="1">
         <v>0</v>
@@ -8727,7 +8727,7 @@
         <v>1001</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C403" s="1">
         <v>0</v>
@@ -8739,7 +8739,7 @@
         <v>1002</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C404" s="1">
         <v>0</v>
@@ -8751,7 +8751,7 @@
         <v>1020</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C405" s="1">
         <v>0</v>
@@ -8763,7 +8763,7 @@
         <v>1040</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C406" s="1">
         <v>0</v>
@@ -8775,7 +8775,7 @@
         <v>1041</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C407" s="1">
         <v>0</v>
@@ -8787,7 +8787,7 @@
         <v>1042</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C408" s="1">
         <v>0</v>
@@ -8799,7 +8799,7 @@
         <v>1043</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C409" s="1">
         <v>0</v>
@@ -8811,7 +8811,7 @@
         <v>1044</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C410" s="1">
         <v>0</v>
@@ -8823,7 +8823,7 @@
         <v>1045</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C411" s="1">
         <v>0</v>
@@ -8835,7 +8835,7 @@
         <v>1046</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C412" s="1">
         <v>0</v>
@@ -8847,7 +8847,7 @@
         <v>1047</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C413" s="1">
         <v>0</v>
@@ -8859,7 +8859,7 @@
         <v>1048</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C414" s="1">
         <v>0</v>
@@ -8871,7 +8871,7 @@
         <v>1049</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C415" s="1">
         <v>0</v>
@@ -8883,7 +8883,7 @@
         <v>1050</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C416" s="1">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>1060</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C417" s="1">
         <v>0</v>
@@ -8907,7 +8907,7 @@
         <v>1061</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C418" s="1">
         <v>0</v>
@@ -8919,7 +8919,7 @@
         <v>1062</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C419" s="1">
         <v>0</v>
@@ -8931,7 +8931,7 @@
         <v>1063</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C420" s="1">
         <v>0</v>
@@ -8943,7 +8943,7 @@
         <v>1064</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C421" s="1">
         <v>0</v>
@@ -8955,7 +8955,7 @@
         <v>1065</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C422" s="1">
         <v>0</v>
@@ -8967,7 +8967,7 @@
         <v>1086</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C423" s="1">
         <v>0</v>
@@ -8979,7 +8979,7 @@
         <v>1087</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C424" s="1">
         <v>0</v>
@@ -8991,7 +8991,7 @@
         <v>1100</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C425" s="1">
         <v>0</v>
@@ -9003,7 +9003,7 @@
         <v>1101</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C426" s="1">
         <v>0</v>
@@ -9015,7 +9015,7 @@
         <v>1102</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C427" s="1">
         <v>0</v>
@@ -9027,7 +9027,7 @@
         <v>1103</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C428" s="1">
         <v>0</v>
@@ -9039,7 +9039,7 @@
         <v>1104</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C429" s="1">
         <v>0</v>
@@ -9051,7 +9051,7 @@
         <v>1105</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C430" s="1">
         <v>0</v>
@@ -9063,7 +9063,7 @@
         <v>1106</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C431" s="1">
         <v>0</v>
@@ -9075,7 +9075,7 @@
         <v>1107</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C432" s="1">
         <v>0</v>
@@ -9087,7 +9087,7 @@
         <v>1108</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C433" s="1">
         <v>0</v>
@@ -9099,7 +9099,7 @@
         <v>1109</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C434" s="1">
         <v>0</v>
@@ -9111,7 +9111,7 @@
         <v>1110</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C435" s="1">
         <v>0</v>
@@ -9123,7 +9123,7 @@
         <v>1111</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C436" s="1">
         <v>0</v>
@@ -9135,7 +9135,7 @@
         <v>1112</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C437" s="1">
         <v>0</v>
@@ -9147,7 +9147,7 @@
         <v>1113</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C438" s="1">
         <v>0</v>
@@ -9159,7 +9159,7 @@
         <v>1114</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C439" s="1">
         <v>0</v>
@@ -9171,7 +9171,7 @@
         <v>1115</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C440" s="1">
         <v>0</v>
@@ -9183,7 +9183,7 @@
         <v>1116</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C441" s="1">
         <v>0</v>
@@ -9195,7 +9195,7 @@
         <v>1117</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C442" s="1">
         <v>0</v>
@@ -9207,7 +9207,7 @@
         <v>1118</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C443" s="1">
         <v>0</v>
@@ -9219,7 +9219,7 @@
         <v>1119</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C444" s="1">
         <v>0</v>
@@ -9231,7 +9231,7 @@
         <v>1120</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C445" s="1">
         <v>0</v>
@@ -9243,7 +9243,7 @@
         <v>1121</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C446" s="1">
         <v>0</v>
@@ -9255,7 +9255,7 @@
         <v>1140</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C447" s="1">
         <v>0</v>
@@ -9267,7 +9267,7 @@
         <v>1141</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C448" s="1">
         <v>0</v>
@@ -9279,7 +9279,7 @@
         <v>1142</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C449" s="1">
         <v>0</v>
@@ -9291,7 +9291,7 @@
         <v>1143</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C450" s="1">
         <v>0</v>
@@ -9303,7 +9303,7 @@
         <v>1144</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C451" s="1">
         <v>0</v>
@@ -9315,7 +9315,7 @@
         <v>1145</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C452" s="1">
         <v>0</v>
@@ -9327,7 +9327,7 @@
         <v>1146</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C453" s="1">
         <v>0</v>
@@ -9339,7 +9339,7 @@
         <v>1147</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C454" s="1">
         <v>0</v>
@@ -9351,7 +9351,7 @@
         <v>1148</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C455" s="1">
         <v>0</v>
@@ -9363,7 +9363,7 @@
         <v>1149</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C456" s="1">
         <v>0</v>
@@ -9375,7 +9375,7 @@
         <v>1150</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C457" s="1">
         <v>0</v>
@@ -9387,7 +9387,7 @@
         <v>1151</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C458" s="1">
         <v>0</v>
@@ -9399,7 +9399,7 @@
         <v>1152</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C459" s="1">
         <v>0</v>
@@ -9411,7 +9411,7 @@
         <v>1153</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C460" s="1">
         <v>0</v>
@@ -9423,7 +9423,7 @@
         <v>1154</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C461" s="1">
         <v>0</v>
@@ -9435,7 +9435,7 @@
         <v>1155</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C462" s="1">
         <v>0</v>
@@ -9447,7 +9447,7 @@
         <v>1156</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C463" s="1">
         <v>0</v>
@@ -9459,7 +9459,7 @@
         <v>1157</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C464" s="1">
         <v>0</v>
@@ -9471,7 +9471,7 @@
         <v>1158</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C465" s="1">
         <v>0</v>
@@ -9483,7 +9483,7 @@
         <v>1159</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C466" s="1">
         <v>0</v>
@@ -9495,7 +9495,7 @@
         <v>1160</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C467" s="1">
         <v>0</v>
@@ -9507,7 +9507,7 @@
         <v>1161</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C468" s="1">
         <v>0</v>
@@ -9519,7 +9519,7 @@
         <v>1162</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C469" s="1">
         <v>0</v>
@@ -9531,7 +9531,7 @@
         <v>1163</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C470" s="1">
         <v>0</v>
@@ -9543,7 +9543,7 @@
         <v>1164</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C471" s="1">
         <v>0</v>
@@ -9555,7 +9555,7 @@
         <v>1165</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C472" s="1">
         <v>0</v>
@@ -9567,7 +9567,7 @@
         <v>1166</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C473" s="1">
         <v>0</v>
@@ -9579,7 +9579,7 @@
         <v>1167</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C474" s="1">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>1168</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C475" s="1">
         <v>0</v>
@@ -9603,7 +9603,7 @@
         <v>1169</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C476" s="1">
         <v>0</v>
@@ -9615,7 +9615,7 @@
         <v>1170</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C477" s="1">
         <v>0</v>
@@ -9627,7 +9627,7 @@
         <v>1171</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C478" s="1">
         <v>0</v>
@@ -9639,7 +9639,7 @@
         <v>1172</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C479" s="1">
         <v>0</v>
@@ -9651,7 +9651,7 @@
         <v>1173</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C480" s="1">
         <v>0</v>
@@ -9663,7 +9663,7 @@
         <v>1174</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C481" s="1">
         <v>0</v>
@@ -9675,7 +9675,7 @@
         <v>1175</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C482" s="1">
         <v>0</v>
@@ -9687,7 +9687,7 @@
         <v>1180</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C483" s="1">
         <v>0</v>
@@ -9699,7 +9699,7 @@
         <v>1181</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C484" s="1">
         <v>0</v>
@@ -9711,7 +9711,7 @@
         <v>1182</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C485" s="1">
         <v>0</v>
@@ -9723,7 +9723,7 @@
         <v>1183</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C486" s="1">
         <v>0</v>
@@ -9735,7 +9735,7 @@
         <v>1184</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C487" s="1">
         <v>0</v>
@@ -9747,7 +9747,7 @@
         <v>1185</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C488" s="1">
         <v>0</v>
@@ -9759,7 +9759,7 @@
         <v>1222</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C489" s="1">
         <v>0</v>
@@ -9771,7 +9771,7 @@
         <v>1223</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C490" s="1">
         <v>0</v>
@@ -9783,7 +9783,7 @@
         <v>1224</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C491" s="1">
         <v>0</v>
@@ -9795,7 +9795,7 @@
         <v>1225</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C492" s="1">
         <v>0</v>
@@ -9807,7 +9807,7 @@
         <v>1226</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C493" s="1">
         <v>0</v>
@@ -9819,7 +9819,7 @@
         <v>1227</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C494" s="1">
         <v>0</v>
@@ -9831,7 +9831,7 @@
         <v>1228</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C495" s="1">
         <v>0</v>
@@ -9843,7 +9843,7 @@
         <v>1229</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C496" s="1">
         <v>0</v>
@@ -9855,7 +9855,7 @@
         <v>1230</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C497" s="1">
         <v>0</v>
@@ -9867,7 +9867,7 @@
         <v>1231</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C498" s="1">
         <v>0</v>
@@ -9879,7 +9879,7 @@
         <v>1232</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C499" s="1">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>1233</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C500" s="1">
         <v>0</v>
@@ -9903,7 +9903,7 @@
         <v>1234</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C501" s="1">
         <v>0</v>
@@ -9915,7 +9915,7 @@
         <v>1235</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C502" s="1">
         <v>0</v>
@@ -9927,7 +9927,7 @@
         <v>1236</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C503" s="1">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>1237</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C504" s="1">
         <v>0</v>
@@ -9951,7 +9951,7 @@
         <v>1238</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C505" s="1">
         <v>0</v>
@@ -9963,7 +9963,7 @@
         <v>1239</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C506" s="1">
         <v>0</v>
@@ -9975,7 +9975,7 @@
         <v>1240</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C507" s="1">
         <v>0</v>
@@ -9987,7 +9987,7 @@
         <v>1241</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C508" s="1">
         <v>0</v>
@@ -9999,7 +9999,7 @@
         <v>1242</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C509" s="1">
         <v>0</v>
@@ -10011,7 +10011,7 @@
         <v>1243</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C510" s="1">
         <v>0</v>
@@ -10023,7 +10023,7 @@
         <v>1244</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C511" s="1">
         <v>0</v>
@@ -10035,7 +10035,7 @@
         <v>1245</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C512" s="1">
         <v>0</v>
@@ -10047,7 +10047,7 @@
         <v>1246</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C513" s="1">
         <v>0</v>
@@ -10059,7 +10059,7 @@
         <v>1247</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C514" s="1">
         <v>0</v>
@@ -10071,7 +10071,7 @@
         <v>1248</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C515" s="1">
         <v>0</v>
@@ -10083,7 +10083,7 @@
         <v>1262</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C516" s="1">
         <v>0</v>
@@ -10095,7 +10095,7 @@
         <v>1263</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C517" s="1">
         <v>0</v>
@@ -10107,7 +10107,7 @@
         <v>1264</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C518" s="1">
         <v>0</v>
@@ -10119,7 +10119,7 @@
         <v>1265</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C519" s="1">
         <v>0</v>
@@ -10131,7 +10131,7 @@
         <v>1266</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C520" s="1">
         <v>0</v>
@@ -10143,7 +10143,7 @@
         <v>1267</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C521" s="1">
         <v>0</v>
@@ -10155,7 +10155,7 @@
         <v>1268</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C522" s="1">
         <v>0</v>
@@ -10167,7 +10167,7 @@
         <v>1269</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C523" s="1">
         <v>0</v>
@@ -10179,7 +10179,7 @@
         <v>1270</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C524" s="1">
         <v>0</v>
@@ -10191,7 +10191,7 @@
         <v>1271</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C525" s="1">
         <v>0</v>
@@ -10203,7 +10203,7 @@
         <v>1272</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C526" s="1">
         <v>0</v>
@@ -10215,7 +10215,7 @@
         <v>1273</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C527" s="1">
         <v>0</v>
@@ -10227,7 +10227,7 @@
         <v>1274</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C528" s="1">
         <v>0</v>
@@ -10239,7 +10239,7 @@
         <v>1275</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C529" s="1">
         <v>0</v>
@@ -10251,7 +10251,7 @@
         <v>1276</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C530" s="1">
         <v>0</v>
@@ -10263,7 +10263,7 @@
         <v>1277</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C531" s="1">
         <v>0</v>
@@ -10275,7 +10275,7 @@
         <v>1278</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C532" s="1">
         <v>0</v>
@@ -10287,7 +10287,7 @@
         <v>1279</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C533" s="1">
         <v>0</v>
@@ -10299,7 +10299,7 @@
         <v>1280</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C534" s="1">
         <v>0</v>
@@ -10311,7 +10311,7 @@
         <v>1281</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C535" s="1">
         <v>0</v>
@@ -10323,7 +10323,7 @@
         <v>1282</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C536" s="1">
         <v>0</v>
@@ -10335,7 +10335,7 @@
         <v>1283</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C537" s="1">
         <v>0</v>
@@ -10347,7 +10347,7 @@
         <v>1284</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C538" s="1">
         <v>0</v>
@@ -10359,7 +10359,7 @@
         <v>1285</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C539" s="1">
         <v>0</v>
@@ -10371,7 +10371,7 @@
         <v>1286</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C540" s="1">
         <v>0</v>
@@ -10383,7 +10383,7 @@
         <v>1287</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C541" s="1">
         <v>0</v>
@@ -10395,7 +10395,7 @@
         <v>1288</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C542" s="1">
         <v>0</v>
@@ -10407,7 +10407,7 @@
         <v>1289</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C543" s="1">
         <v>0</v>
@@ -10419,7 +10419,7 @@
         <v>1290</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C544" s="1">
         <v>0</v>
@@ -10431,7 +10431,7 @@
         <v>1291</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C545" s="1">
         <v>0</v>
@@ -10443,7 +10443,7 @@
         <v>1292</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C546" s="1">
         <v>0</v>
@@ -10455,7 +10455,7 @@
         <v>1293</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C547" s="1">
         <v>0</v>
@@ -10467,7 +10467,7 @@
         <v>1294</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C548" s="1">
         <v>0</v>
@@ -10479,7 +10479,7 @@
         <v>1295</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C549" s="1">
         <v>0</v>
@@ -10491,7 +10491,7 @@
         <v>1296</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C550" s="1">
         <v>0</v>
@@ -10503,7 +10503,7 @@
         <v>1297</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C551" s="1">
         <v>0</v>
@@ -10515,7 +10515,7 @@
         <v>1298</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C552" s="1">
         <v>0</v>
@@ -10527,7 +10527,7 @@
         <v>1299</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C553" s="1">
         <v>0</v>
@@ -10539,7 +10539,7 @@
         <v>1300</v>
       </c>
       <c r="B554" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C554" s="1">
         <v>0</v>
@@ -10551,7 +10551,7 @@
         <v>1301</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C555" s="1">
         <v>0</v>
@@ -10563,7 +10563,7 @@
         <v>1302</v>
       </c>
       <c r="B556" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C556" s="1">
         <v>0</v>
@@ -10575,7 +10575,7 @@
         <v>1303</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C557" s="1">
         <v>0</v>
@@ -10587,7 +10587,7 @@
         <v>1304</v>
       </c>
       <c r="B558" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C558" s="1">
         <v>0</v>
@@ -10599,7 +10599,7 @@
         <v>1305</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C559" s="1">
         <v>0</v>
@@ -10611,7 +10611,7 @@
         <v>1306</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C560" s="1">
         <v>0</v>
@@ -10623,7 +10623,7 @@
         <v>1307</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C561" s="1">
         <v>0</v>
@@ -10635,7 +10635,7 @@
         <v>1308</v>
       </c>
       <c r="B562" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C562" s="1">
         <v>0</v>
@@ -10647,7 +10647,7 @@
         <v>1309</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C563" s="1">
         <v>0</v>
@@ -10659,7 +10659,7 @@
         <v>1322</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C564" s="1">
         <v>0</v>
@@ -10671,7 +10671,7 @@
         <v>1323</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C565" s="1">
         <v>0</v>
@@ -10683,7 +10683,7 @@
         <v>1324</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C566" s="1">
         <v>0</v>
@@ -10695,7 +10695,7 @@
         <v>1325</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C567" s="1">
         <v>0</v>
@@ -10707,7 +10707,7 @@
         <v>1326</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C568" s="1">
         <v>0</v>
@@ -10719,7 +10719,7 @@
         <v>1327</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C569" s="1">
         <v>0</v>
@@ -10731,7 +10731,7 @@
         <v>1328</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C570" s="1">
         <v>0</v>
@@ -10743,7 +10743,7 @@
         <v>1329</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C571" s="1">
         <v>0</v>
@@ -10755,7 +10755,7 @@
         <v>1330</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C572" s="1">
         <v>0</v>
@@ -10767,7 +10767,7 @@
         <v>1331</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C573" s="1">
         <v>0</v>
@@ -10779,7 +10779,7 @@
         <v>1332</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C574" s="1">
         <v>0</v>
@@ -10791,7 +10791,7 @@
         <v>1333</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C575" s="1">
         <v>0</v>
@@ -10803,7 +10803,7 @@
         <v>1334</v>
       </c>
       <c r="B576" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C576" s="1">
         <v>0</v>
@@ -10815,7 +10815,7 @@
         <v>1335</v>
       </c>
       <c r="B577" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C577" s="1">
         <v>0</v>
@@ -10827,7 +10827,7 @@
         <v>1336</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C578" s="1">
         <v>0</v>
@@ -10839,7 +10839,7 @@
         <v>1337</v>
       </c>
       <c r="B579" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C579" s="1">
         <v>0</v>
@@ -10851,7 +10851,7 @@
         <v>1338</v>
       </c>
       <c r="B580" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C580" s="1">
         <v>0</v>
@@ -10863,7 +10863,7 @@
         <v>1339</v>
       </c>
       <c r="B581" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C581" s="1">
         <v>0</v>
@@ -10875,7 +10875,7 @@
         <v>1340</v>
       </c>
       <c r="B582" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C582" s="1">
         <v>0</v>
@@ -10887,7 +10887,7 @@
         <v>1341</v>
       </c>
       <c r="B583" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C583" s="1">
         <v>0</v>
@@ -10899,7 +10899,7 @@
         <v>1342</v>
       </c>
       <c r="B584" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C584" s="1">
         <v>0</v>
@@ -10911,7 +10911,7 @@
         <v>1343</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C585" s="1">
         <v>0</v>
@@ -10923,7 +10923,7 @@
         <v>1344</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C586" s="1">
         <v>0</v>
@@ -10935,7 +10935,7 @@
         <v>1345</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C587" s="1">
         <v>0</v>
@@ -10947,7 +10947,7 @@
         <v>1346</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C588" s="1">
         <v>0</v>
@@ -10959,7 +10959,7 @@
         <v>1347</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C589" s="1">
         <v>0</v>
@@ -10971,7 +10971,7 @@
         <v>1348</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C590" s="1">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>1349</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C591" s="1">
         <v>0</v>
@@ -10995,7 +10995,7 @@
         <v>1350</v>
       </c>
       <c r="B592" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C592" s="1">
         <v>0</v>
@@ -11007,7 +11007,7 @@
         <v>1351</v>
       </c>
       <c r="B593" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C593" s="1">
         <v>0</v>
@@ -11019,7 +11019,7 @@
         <v>1352</v>
       </c>
       <c r="B594" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C594" s="1">
         <v>0</v>
@@ -11031,7 +11031,7 @@
         <v>1353</v>
       </c>
       <c r="B595" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C595" s="1">
         <v>0</v>
@@ -11043,7 +11043,7 @@
         <v>1354</v>
       </c>
       <c r="B596" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C596" s="1">
         <v>0</v>
@@ -11055,7 +11055,7 @@
         <v>1362</v>
       </c>
       <c r="B597" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C597" s="1">
         <v>0</v>
@@ -11067,7 +11067,7 @@
         <v>1363</v>
       </c>
       <c r="B598" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C598" s="1">
         <v>0</v>
@@ -11079,7 +11079,7 @@
         <v>1364</v>
       </c>
       <c r="B599" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C599" s="1">
         <v>0</v>
@@ -11091,7 +11091,7 @@
         <v>1365</v>
       </c>
       <c r="B600" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C600" s="1">
         <v>0</v>
@@ -11103,7 +11103,7 @@
         <v>1366</v>
       </c>
       <c r="B601" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C601" s="1">
         <v>0</v>
@@ -11115,7 +11115,7 @@
         <v>1367</v>
       </c>
       <c r="B602" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C602" s="1">
         <v>0</v>
@@ -11127,7 +11127,7 @@
         <v>1368</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C603" s="1">
         <v>0</v>
@@ -11139,7 +11139,7 @@
         <v>1369</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C604" s="1">
         <v>0</v>
@@ -11151,7 +11151,7 @@
         <v>1370</v>
       </c>
       <c r="B605" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C605" s="1">
         <v>0</v>
@@ -11163,7 +11163,7 @@
         <v>1371</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C606" s="1">
         <v>0</v>
@@ -11175,7 +11175,7 @@
         <v>1382</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C607" s="1">
         <v>0</v>
@@ -11187,7 +11187,7 @@
         <v>1422</v>
       </c>
       <c r="B608" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C608" s="1">
         <v>0</v>
@@ -11199,7 +11199,7 @@
         <v>1462</v>
       </c>
       <c r="B609" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C609" s="1">
         <v>0</v>
@@ -11211,7 +11211,7 @@
         <v>1482</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C610" s="1">
         <v>0</v>
@@ -11223,7 +11223,7 @@
         <v>1483</v>
       </c>
       <c r="B611" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C611" s="1">
         <v>0</v>
@@ -11235,7 +11235,7 @@
         <v>1484</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C612" s="1">
         <v>0</v>
@@ -11247,7 +11247,7 @@
         <v>1485</v>
       </c>
       <c r="B613" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C613" s="1">
         <v>0</v>
@@ -11259,7 +11259,7 @@
         <v>1486</v>
       </c>
       <c r="B614" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C614" s="1">
         <v>0</v>
@@ -11271,7 +11271,7 @@
         <v>1487</v>
       </c>
       <c r="B615" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C615" s="1">
         <v>0</v>
@@ -11283,7 +11283,7 @@
         <v>1488</v>
       </c>
       <c r="B616" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C616" s="1">
         <v>0</v>
@@ -11295,7 +11295,7 @@
         <v>1502</v>
       </c>
       <c r="B617" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C617" s="1">
         <v>0</v>
@@ -11307,7 +11307,7 @@
         <v>1503</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C618" s="1">
         <v>0</v>
@@ -11319,7 +11319,7 @@
         <v>1504</v>
       </c>
       <c r="B619" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C619" s="1">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>1505</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C620" s="1">
         <v>0</v>
@@ -11343,7 +11343,7 @@
         <v>1506</v>
       </c>
       <c r="B621" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C621" s="1">
         <v>0</v>
@@ -11355,7 +11355,7 @@
         <v>1507</v>
       </c>
       <c r="B622" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C622" s="1">
         <v>0</v>
@@ -11367,7 +11367,7 @@
         <v>1508</v>
       </c>
       <c r="B623" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C623" s="1">
         <v>0</v>
@@ -11379,7 +11379,7 @@
         <v>1509</v>
       </c>
       <c r="B624" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C624" s="1">
         <v>0</v>
@@ -11391,7 +11391,7 @@
         <v>1510</v>
       </c>
       <c r="B625" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C625" s="1">
         <v>0</v>
@@ -11403,7 +11403,7 @@
         <v>1511</v>
       </c>
       <c r="B626" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C626" s="1">
         <v>0</v>
@@ -11415,7 +11415,7 @@
         <v>1542</v>
       </c>
       <c r="B627" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C627" s="1">
         <v>0</v>
@@ -11427,7 +11427,7 @@
         <v>1562</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C628" s="1">
         <v>0</v>
@@ -11439,7 +11439,7 @@
         <v>1563</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C629" s="1">
         <v>0</v>
@@ -11451,7 +11451,7 @@
         <v>1564</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C630" s="1">
         <v>0</v>
@@ -11463,7 +11463,7 @@
         <v>1565</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C631" s="1">
         <v>0</v>
@@ -11475,7 +11475,7 @@
         <v>1566</v>
       </c>
       <c r="B632" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C632" s="1">
         <v>0</v>
@@ -11487,7 +11487,7 @@
         <v>1567</v>
       </c>
       <c r="B633" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C633" s="1">
         <v>0</v>
@@ -11499,7 +11499,7 @@
         <v>1568</v>
       </c>
       <c r="B634" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C634" s="1">
         <v>0</v>
@@ -11511,7 +11511,7 @@
         <v>1569</v>
       </c>
       <c r="B635" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C635" s="1">
         <v>0</v>
@@ -11523,7 +11523,7 @@
         <v>1570</v>
       </c>
       <c r="B636" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C636" s="1">
         <v>0</v>
@@ -11535,7 +11535,7 @@
         <v>1571</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C637" s="1">
         <v>0</v>
@@ -11547,7 +11547,7 @@
         <v>1572</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C638" s="1">
         <v>0</v>
@@ -11559,7 +11559,7 @@
         <v>1573</v>
       </c>
       <c r="B639" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C639" s="1">
         <v>0</v>
@@ -11571,7 +11571,7 @@
         <v>1574</v>
       </c>
       <c r="B640" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C640" s="1">
         <v>0</v>
@@ -11583,7 +11583,7 @@
         <v>1575</v>
       </c>
       <c r="B641" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C641" s="1">
         <v>0</v>
@@ -11595,7 +11595,7 @@
         <v>1576</v>
       </c>
       <c r="B642" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C642" s="1">
         <v>0</v>
@@ -11607,7 +11607,7 @@
         <v>1577</v>
       </c>
       <c r="B643" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C643" s="1">
         <v>0</v>
@@ -11619,7 +11619,7 @@
         <v>1578</v>
       </c>
       <c r="B644" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C644" s="1">
         <v>0</v>
@@ -11631,7 +11631,7 @@
         <v>1579</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C645" s="1">
         <v>0</v>
@@ -11643,7 +11643,7 @@
         <v>1580</v>
       </c>
       <c r="B646" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C646" s="1">
         <v>0</v>
@@ -11655,7 +11655,7 @@
         <v>1581</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C647" s="1">
         <v>0</v>
@@ -11667,7 +11667,7 @@
         <v>1582</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C648" s="1">
         <v>0</v>
@@ -11679,7 +11679,7 @@
         <v>1583</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C649" s="1">
         <v>0</v>
@@ -11691,7 +11691,7 @@
         <v>1584</v>
       </c>
       <c r="B650" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C650" s="1">
         <v>0</v>
@@ -11703,7 +11703,7 @@
         <v>1585</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C651" s="1">
         <v>0</v>
@@ -11715,7 +11715,7 @@
         <v>1586</v>
       </c>
       <c r="B652" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C652" s="1">
         <v>0</v>
@@ -11727,7 +11727,7 @@
         <v>1587</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C653" s="1">
         <v>0</v>
@@ -11739,7 +11739,7 @@
         <v>1588</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C654" s="1">
         <v>0</v>
@@ -11751,7 +11751,7 @@
         <v>1589</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C655" s="1">
         <v>0</v>
@@ -11763,7 +11763,7 @@
         <v>1590</v>
       </c>
       <c r="B656" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C656" s="1">
         <v>0</v>
@@ -11775,7 +11775,7 @@
         <v>1591</v>
       </c>
       <c r="B657" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C657" s="1">
         <v>0</v>
@@ -11787,7 +11787,7 @@
         <v>1592</v>
       </c>
       <c r="B658" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C658" s="1">
         <v>0</v>
@@ -11799,7 +11799,7 @@
         <v>1593</v>
       </c>
       <c r="B659" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C659" s="1">
         <v>0</v>
@@ -11811,7 +11811,7 @@
         <v>1594</v>
       </c>
       <c r="B660" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C660" s="1">
         <v>0</v>
@@ -11823,7 +11823,7 @@
         <v>1595</v>
       </c>
       <c r="B661" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C661" s="1">
         <v>0</v>
@@ -11835,7 +11835,7 @@
         <v>1596</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C662" s="1">
         <v>0</v>
@@ -11847,7 +11847,7 @@
         <v>1597</v>
       </c>
       <c r="B663" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C663" s="1">
         <v>0</v>
@@ -11859,7 +11859,7 @@
         <v>1622</v>
       </c>
       <c r="B664" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C664" s="1">
         <v>0</v>
@@ -11871,7 +11871,7 @@
         <v>1642</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C665" s="1">
         <v>0</v>
@@ -11883,7 +11883,7 @@
         <v>1682</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C666" s="1">
         <v>0</v>
@@ -11895,7 +11895,7 @@
         <v>1742</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C667" s="1">
         <v>0</v>
@@ -11907,7 +11907,7 @@
         <v>1762</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C668" s="1">
         <v>0</v>
@@ -11919,7 +11919,7 @@
         <v>1782</v>
       </c>
       <c r="B669" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C669" s="1">
         <v>0</v>
@@ -11931,7 +11931,7 @@
         <v>1802</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C670" s="1">
         <v>0</v>
@@ -11943,7 +11943,7 @@
         <v>1803</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C671" s="1">
         <v>0</v>
@@ -11955,7 +11955,7 @@
         <v>1804</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C672" s="1">
         <v>0</v>
@@ -11967,7 +11967,7 @@
         <v>1805</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C673" s="1">
         <v>0</v>
@@ -11979,7 +11979,7 @@
         <v>1806</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C674" s="1">
         <v>0</v>
@@ -11991,7 +11991,7 @@
         <v>1807</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C675" s="1">
         <v>0</v>
@@ -12003,7 +12003,7 @@
         <v>1808</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C676" s="1">
         <v>0</v>
@@ -12015,7 +12015,7 @@
         <v>1809</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C677" s="1">
         <v>0</v>
@@ -12027,7 +12027,7 @@
         <v>1810</v>
       </c>
       <c r="B678" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C678" s="1">
         <v>0</v>
@@ -12039,7 +12039,7 @@
         <v>1811</v>
       </c>
       <c r="B679" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C679" s="1">
         <v>0</v>
@@ -12051,7 +12051,7 @@
         <v>1812</v>
       </c>
       <c r="B680" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C680" s="1">
         <v>0</v>
@@ -12063,7 +12063,7 @@
         <v>1813</v>
       </c>
       <c r="B681" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C681" s="1">
         <v>0</v>
@@ -12075,7 +12075,7 @@
         <v>1814</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C682" s="1">
         <v>0</v>
@@ -12087,7 +12087,7 @@
         <v>1815</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C683" s="1">
         <v>0</v>
@@ -12099,7 +12099,7 @@
         <v>1816</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C684" s="1">
         <v>0</v>
@@ -12111,7 +12111,7 @@
         <v>1817</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C685" s="1">
         <v>0</v>
@@ -12123,7 +12123,7 @@
         <v>1818</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C686" s="1">
         <v>0</v>
@@ -12135,7 +12135,7 @@
         <v>1819</v>
       </c>
       <c r="B687" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C687" s="1">
         <v>0</v>
@@ -12147,7 +12147,7 @@
         <v>1820</v>
       </c>
       <c r="B688" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="C688" s="1">
         <v>0</v>
@@ -12159,7 +12159,7 @@
         <v>1821</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="C689" s="1">
         <v>0</v>
@@ -12171,7 +12171,7 @@
         <v>1822</v>
       </c>
       <c r="B690" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C690" s="1">
         <v>0</v>
@@ -12183,7 +12183,7 @@
         <v>1823</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C691" s="1">
         <v>0</v>
@@ -12195,7 +12195,7 @@
         <v>1842</v>
       </c>
       <c r="B692" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C692" s="1">
         <v>0</v>
@@ -12207,7 +12207,7 @@
         <v>1922</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C693" s="1">
         <v>0</v>
@@ -12219,7 +12219,7 @@
         <v>1942</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C694" s="1">
         <v>0</v>
@@ -12231,7 +12231,7 @@
         <v>1943</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C695" s="1">
         <v>0</v>
@@ -12243,7 +12243,7 @@
         <v>1944</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C696" s="1">
         <v>0</v>
@@ -12255,7 +12255,7 @@
         <v>1962</v>
       </c>
       <c r="B697" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C697" s="1">
         <v>0</v>
@@ -12267,7 +12267,7 @@
         <v>2002</v>
       </c>
       <c r="B698" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C698" s="1">
         <v>0</v>
@@ -12279,7 +12279,7 @@
         <v>2003</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C699" s="1">
         <v>0</v>
@@ -12291,7 +12291,7 @@
         <v>2042</v>
       </c>
       <c r="B700" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C700" s="1">
         <v>0</v>
@@ -12303,7 +12303,7 @@
         <v>2062</v>
       </c>
       <c r="B701" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C701" s="1">
         <v>0</v>
@@ -12315,7 +12315,7 @@
         <v>2082</v>
       </c>
       <c r="B702" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C702" s="1">
         <v>0</v>
@@ -12327,7 +12327,7 @@
         <v>2104</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C703" s="1">
         <v>0</v>
@@ -12339,7 +12339,7 @@
         <v>2222</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C704" s="1">
         <v>0</v>
@@ -12351,7 +12351,7 @@
         <v>2223</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C705" s="1">
         <v>0</v>
@@ -12363,7 +12363,7 @@
         <v>2225</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C706" s="1">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>2226</v>
       </c>
       <c r="B707" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C707" s="1">
         <v>0</v>
@@ -12387,7 +12387,7 @@
         <v>2227</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C708" s="1">
         <v>0</v>
@@ -12399,7 +12399,7 @@
         <v>2228</v>
       </c>
       <c r="B709" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C709" s="1">
         <v>0</v>
@@ -12411,7 +12411,7 @@
         <v>2229</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C710" s="1">
         <v>0</v>
@@ -12423,7 +12423,7 @@
         <v>2230</v>
       </c>
       <c r="B711" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C711" s="1">
         <v>0</v>
@@ -12435,7 +12435,7 @@
         <v>2242</v>
       </c>
       <c r="B712" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C712" s="1">
         <v>0</v>
@@ -12447,7 +12447,7 @@
         <v>2243</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C713" s="1">
         <v>0</v>
@@ -12459,7 +12459,7 @@
         <v>2244</v>
       </c>
       <c r="B714" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C714" s="1">
         <v>0</v>
@@ -12471,7 +12471,7 @@
         <v>2245</v>
       </c>
       <c r="B715" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C715" s="1">
         <v>0</v>
@@ -12483,7 +12483,7 @@
         <v>2262</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C716" s="1">
         <v>0</v>
@@ -12495,7 +12495,7 @@
         <v>2263</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C717" s="1">
         <v>0</v>
@@ -12507,7 +12507,7 @@
         <v>2264</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C718" s="1">
         <v>0</v>
@@ -12519,7 +12519,7 @@
         <v>2282</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C719" s="1">
         <v>0</v>
@@ -12531,7 +12531,7 @@
         <v>2302</v>
       </c>
       <c r="B720" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C720" s="1">
         <v>0</v>
@@ -12543,7 +12543,7 @@
         <v>2362</v>
       </c>
       <c r="B721" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C721" s="1">
         <v>0</v>
@@ -12555,7 +12555,7 @@
         <v>2402</v>
       </c>
       <c r="B722" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C722" s="1">
         <v>0</v>
@@ -12567,7 +12567,7 @@
         <v>2442</v>
       </c>
       <c r="B723" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C723" s="1">
         <v>0</v>
@@ -12579,7 +12579,7 @@
         <v>2443</v>
       </c>
       <c r="B724" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C724" s="1">
         <v>0</v>
@@ -12591,7 +12591,7 @@
         <v>2462</v>
       </c>
       <c r="B725" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C725" s="1">
         <v>0</v>
@@ -12603,7 +12603,7 @@
         <v>2482</v>
       </c>
       <c r="B726" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C726" s="1">
         <v>0</v>
@@ -12615,7 +12615,7 @@
         <v>2522</v>
       </c>
       <c r="B727" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C727" s="1">
         <v>0</v>
@@ -12627,7 +12627,7 @@
         <v>2542</v>
       </c>
       <c r="B728" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C728" s="1">
         <v>0</v>
@@ -12639,7 +12639,7 @@
         <v>2582</v>
       </c>
       <c r="B729" s="2" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C729" s="1">
         <v>0</v>
@@ -12651,7 +12651,7 @@
         <v>2583</v>
       </c>
       <c r="B730" s="2" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C730" s="1">
         <v>0</v>
@@ -12663,7 +12663,7 @@
         <v>2602</v>
       </c>
       <c r="B731" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C731" s="1">
         <v>0</v>
@@ -12675,7 +12675,7 @@
         <v>2605</v>
       </c>
       <c r="B732" s="2" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C732" s="1">
         <v>0</v>
@@ -12687,7 +12687,7 @@
         <v>2642</v>
       </c>
       <c r="B733" s="2" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C733" s="1">
         <v>0</v>
@@ -12699,7 +12699,7 @@
         <v>2682</v>
       </c>
       <c r="B734" s="2" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="C734" s="1">
         <v>0</v>
@@ -12711,7 +12711,7 @@
         <v>2702</v>
       </c>
       <c r="B735" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C735" s="1">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>2742</v>
       </c>
       <c r="B736" s="2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C736" s="1">
         <v>0</v>
@@ -12735,7 +12735,7 @@
         <v>2743</v>
       </c>
       <c r="B737" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C737" s="1">
         <v>0</v>
@@ -12747,7 +12747,7 @@
         <v>2762</v>
       </c>
       <c r="B738" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C738" s="1">
         <v>0</v>
@@ -12759,7 +12759,7 @@
         <v>2763</v>
       </c>
       <c r="B739" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C739" s="1">
         <v>0</v>
@@ -12771,7 +12771,7 @@
         <v>2764</v>
       </c>
       <c r="B740" s="2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C740" s="1">
         <v>0</v>
@@ -12783,7 +12783,7 @@
         <v>2765</v>
       </c>
       <c r="B741" s="2" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C741" s="1">
         <v>0</v>
@@ -12795,7 +12795,7 @@
         <v>2766</v>
       </c>
       <c r="B742" s="2" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C742" s="1">
         <v>0</v>
@@ -12807,7 +12807,7 @@
         <v>2767</v>
       </c>
       <c r="B743" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C743" s="1">
         <v>0</v>
@@ -12819,7 +12819,7 @@
         <v>2782</v>
       </c>
       <c r="B744" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C744" s="1">
         <v>0</v>
@@ -12831,7 +12831,7 @@
         <v>2802</v>
       </c>
       <c r="B745" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C745" s="1">
         <v>0</v>
@@ -12843,7 +12843,7 @@
         <v>2803</v>
       </c>
       <c r="B746" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C746" s="1">
         <v>0</v>
@@ -12855,7 +12855,7 @@
         <v>2804</v>
       </c>
       <c r="B747" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C747" s="1">
         <v>0</v>
@@ -12867,7 +12867,7 @@
         <v>2805</v>
       </c>
       <c r="B748" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C748" s="1">
         <v>0</v>
@@ -12879,7 +12879,7 @@
         <v>2806</v>
       </c>
       <c r="B749" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="C749" s="1">
         <v>0</v>
@@ -12891,7 +12891,7 @@
         <v>2807</v>
       </c>
       <c r="B750" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C750" s="1">
         <v>0</v>
@@ -12903,7 +12903,7 @@
         <v>2808</v>
       </c>
       <c r="B751" s="2" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C751" s="1">
         <v>0</v>
@@ -12915,7 +12915,7 @@
         <v>2809</v>
       </c>
       <c r="B752" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C752" s="1">
         <v>0</v>
@@ -12927,7 +12927,7 @@
         <v>2842</v>
       </c>
       <c r="B753" s="2" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C753" s="1">
         <v>0</v>
@@ -12939,7 +12939,7 @@
         <v>2862</v>
       </c>
       <c r="B754" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C754" s="1">
         <v>0</v>
@@ -12951,7 +12951,7 @@
         <v>2902</v>
       </c>
       <c r="B755" s="2" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C755" s="1">
         <v>0</v>
@@ -12963,7 +12963,7 @@
         <v>3023</v>
       </c>
       <c r="B756" s="2" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C756" s="1">
         <v>0</v>
@@ -12975,7 +12975,7 @@
         <v>3043</v>
       </c>
       <c r="B757" s="2" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="C757" s="1">
         <v>0</v>
@@ -12987,7 +12987,7 @@
         <v>3044</v>
       </c>
       <c r="B758" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C758" s="1">
         <v>0</v>
@@ -12999,7 +12999,7 @@
         <v>3045</v>
       </c>
       <c r="B759" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C759" s="1">
         <v>0</v>
@@ -13011,7 +13011,7 @@
         <v>3046</v>
       </c>
       <c r="B760" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C760" s="1">
         <v>0</v>
@@ -13023,7 +13023,7 @@
         <v>3047</v>
       </c>
       <c r="B761" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C761" s="1">
         <v>0</v>
@@ -13035,7 +13035,7 @@
         <v>3063</v>
       </c>
       <c r="B762" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C762" s="1">
         <v>0</v>
@@ -13047,7 +13047,7 @@
         <v>3065</v>
       </c>
       <c r="B763" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C763" s="1">
         <v>0</v>
@@ -13059,7 +13059,7 @@
         <v>3083</v>
       </c>
       <c r="B764" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="C764" s="1">
         <v>0</v>
@@ -13071,7 +13071,7 @@
         <v>3123</v>
       </c>
       <c r="B765" s="2" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="C765" s="1">
         <v>0</v>
@@ -13083,7 +13083,7 @@
         <v>3124</v>
       </c>
       <c r="B766" s="2" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C766" s="1">
         <v>0</v>
@@ -13095,7 +13095,7 @@
         <v>3125</v>
       </c>
       <c r="B767" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C767" s="1">
         <v>0</v>
@@ -13107,7 +13107,7 @@
         <v>3185</v>
       </c>
       <c r="B768" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C768" s="1">
         <v>0</v>
@@ -13119,7 +13119,7 @@
         <v>3205</v>
       </c>
       <c r="B769" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="C769" s="1">
         <v>0</v>
@@ -13131,7 +13131,7 @@
         <v>3206</v>
       </c>
       <c r="B770" s="2" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C770" s="1">
         <v>0</v>
@@ -13143,7 +13143,7 @@
         <v>3225</v>
       </c>
       <c r="B771" s="2" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="C771" s="1">
         <v>0</v>
@@ -13155,7 +13155,7 @@
         <v>3226</v>
       </c>
       <c r="B772" s="2" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C772" s="1">
         <v>0</v>
@@ -13167,7 +13167,7 @@
         <v>3227</v>
       </c>
       <c r="B773" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C773" s="1">
         <v>0</v>
@@ -13179,7 +13179,7 @@
         <v>3228</v>
       </c>
       <c r="B774" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C774" s="1">
         <v>0</v>
@@ -13191,7 +13191,7 @@
         <v>3229</v>
       </c>
       <c r="B775" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C775" s="1">
         <v>0</v>
@@ -13203,7 +13203,7 @@
         <v>3230</v>
       </c>
       <c r="B776" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="C776" s="1">
         <v>0</v>
@@ -13215,7 +13215,7 @@
         <v>3245</v>
       </c>
       <c r="B777" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="C777" s="1">
         <v>0</v>
@@ -13227,7 +13227,7 @@
         <v>3246</v>
       </c>
       <c r="B778" s="2" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C778" s="1">
         <v>0</v>
@@ -13239,7 +13239,7 @@
         <v>3247</v>
       </c>
       <c r="B779" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="C779" s="1">
         <v>0</v>
@@ -13251,7 +13251,7 @@
         <v>3248</v>
       </c>
       <c r="B780" s="2" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C780" s="1">
         <v>0</v>
@@ -13263,7 +13263,7 @@
         <v>3249</v>
       </c>
       <c r="B781" s="2" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C781" s="1">
         <v>0</v>
@@ -13275,7 +13275,7 @@
         <v>3250</v>
       </c>
       <c r="B782" s="2" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="C782" s="1">
         <v>0</v>
@@ -13287,7 +13287,7 @@
         <v>3251</v>
       </c>
       <c r="B783" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C783" s="1">
         <v>0</v>
@@ -13299,7 +13299,7 @@
         <v>3252</v>
       </c>
       <c r="B784" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C784" s="1">
         <v>0</v>
@@ -13311,7 +13311,7 @@
         <v>3253</v>
       </c>
       <c r="B785" s="2" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C785" s="1">
         <v>0</v>
@@ -13323,7 +13323,7 @@
         <v>3254</v>
       </c>
       <c r="B786" s="2" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C786" s="1">
         <v>0</v>
@@ -13335,7 +13335,7 @@
         <v>3255</v>
       </c>
       <c r="B787" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C787" s="1">
         <v>0</v>
@@ -13347,7 +13347,7 @@
         <v>3305</v>
       </c>
       <c r="B788" s="2" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C788" s="1">
         <v>0</v>
@@ -13359,7 +13359,7 @@
         <v>3306</v>
       </c>
       <c r="B789" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="C789" s="1">
         <v>0</v>
@@ -13371,7 +13371,7 @@
         <v>3325</v>
       </c>
       <c r="B790" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C790" s="1">
         <v>0</v>
@@ -13383,7 +13383,7 @@
         <v>3345</v>
       </c>
       <c r="B791" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C791" s="1">
         <v>0</v>
@@ -13395,7 +13395,7 @@
         <v>3365</v>
       </c>
       <c r="B792" s="2" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C792" s="1">
         <v>0</v>
@@ -13407,7 +13407,7 @@
         <v>3367</v>
       </c>
       <c r="B793" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C793" s="1">
         <v>0</v>
@@ -13419,7 +13419,7 @@
         <v>3368</v>
       </c>
       <c r="B794" s="2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C794" s="1">
         <v>0</v>
@@ -13431,7 +13431,7 @@
         <v>3385</v>
       </c>
       <c r="B795" s="2" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C795" s="1">
         <v>0</v>
@@ -13443,7 +13443,7 @@
         <v>3407</v>
       </c>
       <c r="B796" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C796" s="1">
         <v>0</v>
@@ -13455,7 +13455,7 @@
         <v>3409</v>
       </c>
       <c r="B797" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="C797" s="1">
         <v>0</v>
@@ -13467,7 +13467,7 @@
         <v>3426</v>
       </c>
       <c r="B798" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C798" s="1">
         <v>0</v>
@@ -13479,7 +13479,7 @@
         <v>3445</v>
       </c>
       <c r="B799" s="2" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C799" s="1">
         <v>0</v>
@@ -13491,7 +13491,7 @@
         <v>3485</v>
       </c>
       <c r="B800" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C800" s="1">
         <v>0</v>
@@ -13503,7 +13503,7 @@
         <v>3486</v>
       </c>
       <c r="B801" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C801" s="1">
         <v>0</v>
@@ -13515,7 +13515,7 @@
         <v>3487</v>
       </c>
       <c r="B802" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C802" s="1">
         <v>0</v>
@@ -13527,7 +13527,7 @@
         <v>3488</v>
       </c>
       <c r="B803" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C803" s="1">
         <v>0</v>
@@ -13539,7 +13539,7 @@
         <v>3489</v>
       </c>
       <c r="B804" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C804" s="1">
         <v>0</v>
@@ -13551,7 +13551,7 @@
         <v>3490</v>
       </c>
       <c r="B805" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C805" s="1">
         <v>0</v>
@@ -13563,7 +13563,7 @@
         <v>3491</v>
       </c>
       <c r="B806" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C806" s="1">
         <v>0</v>
@@ -13575,7 +13575,7 @@
         <v>3492</v>
       </c>
       <c r="B807" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C807" s="1">
         <v>0</v>
@@ -13587,7 +13587,7 @@
         <v>3505</v>
       </c>
       <c r="B808" s="2" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C808" s="1">
         <v>0</v>
@@ -13599,7 +13599,7 @@
         <v>3525</v>
       </c>
       <c r="B809" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C809" s="1">
         <v>0</v>
@@ -13611,7 +13611,7 @@
         <v>3545</v>
       </c>
       <c r="B810" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C810" s="1">
         <v>0</v>
@@ -13623,7 +13623,7 @@
         <v>3546</v>
       </c>
       <c r="B811" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C811" s="1">
         <v>0</v>
@@ -13635,7 +13635,7 @@
         <v>3565</v>
       </c>
       <c r="B812" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C812" s="1">
         <v>0</v>
@@ -13647,7 +13647,7 @@
         <v>3585</v>
       </c>
       <c r="B813" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C813" s="1">
         <v>0</v>
@@ -13659,7 +13659,7 @@
         <v>3605</v>
       </c>
       <c r="B814" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="C814" s="1">
         <v>0</v>
@@ -13671,7 +13671,7 @@
         <v>3625</v>
       </c>
       <c r="B815" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C815" s="1">
         <v>0</v>
@@ -13683,7 +13683,7 @@
         <v>3626</v>
       </c>
       <c r="B816" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C816" s="1">
         <v>0</v>
@@ -13695,7 +13695,7 @@
         <v>3627</v>
       </c>
       <c r="B817" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C817" s="1">
         <v>0</v>
@@ -13707,7 +13707,7 @@
         <v>3647</v>
       </c>
       <c r="B818" s="2" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="C818" s="1">
         <v>0</v>
@@ -13719,7 +13719,7 @@
         <v>3648</v>
       </c>
       <c r="B819" s="2" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="C819" s="1">
         <v>0</v>
@@ -13731,7 +13731,7 @@
         <v>3649</v>
       </c>
       <c r="B820" s="2" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="C820" s="1">
         <v>0</v>
@@ -13743,7 +13743,7 @@
         <v>3650</v>
       </c>
       <c r="B821" s="2" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C821" s="1">
         <v>0</v>
@@ -13755,7 +13755,7 @@
         <v>3651</v>
       </c>
       <c r="B822" s="2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C822" s="1">
         <v>0</v>
@@ -13767,7 +13767,7 @@
         <v>3652</v>
       </c>
       <c r="B823" s="2" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C823" s="1">
         <v>0</v>
@@ -13779,7 +13779,7 @@
         <v>3653</v>
       </c>
       <c r="B824" s="2" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="C824" s="1">
         <v>0</v>
@@ -13791,7 +13791,7 @@
         <v>3655</v>
       </c>
       <c r="B825" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="C825" s="1">
         <v>0</v>
@@ -13803,7 +13803,7 @@
         <v>3656</v>
       </c>
       <c r="B826" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="C826" s="1">
         <v>0</v>
@@ -13815,7 +13815,7 @@
         <v>3657</v>
       </c>
       <c r="B827" s="2" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="C827" s="1">
         <v>0</v>
@@ -13827,7 +13827,7 @@
         <v>3658</v>
       </c>
       <c r="B828" s="2" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C828" s="1">
         <v>0</v>
@@ -13839,7 +13839,7 @@
         <v>3659</v>
       </c>
       <c r="B829" s="2" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C829" s="1">
         <v>0</v>
@@ -13851,7 +13851,7 @@
         <v>3660</v>
       </c>
       <c r="B830" s="2" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="C830" s="1">
         <v>0</v>
@@ -13863,7 +13863,7 @@
         <v>3662</v>
       </c>
       <c r="B831" s="2" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C831" s="1">
         <v>0</v>
@@ -13875,7 +13875,7 @@
         <v>3663</v>
       </c>
       <c r="B832" s="2" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="C832" s="1">
         <v>0</v>
@@ -13887,7 +13887,7 @@
         <v>3664</v>
       </c>
       <c r="B833" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C833" s="1">
         <v>0</v>
@@ -13899,7 +13899,7 @@
         <v>3665</v>
       </c>
       <c r="B834" s="2" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C834" s="1">
         <v>0</v>
@@ -13911,7 +13911,7 @@
         <v>3666</v>
       </c>
       <c r="B835" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="C835" s="1">
         <v>0</v>
@@ -13923,7 +13923,7 @@
         <v>3667</v>
       </c>
       <c r="B836" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="C836" s="1">
         <v>0</v>
@@ -13935,7 +13935,7 @@
         <v>3668</v>
       </c>
       <c r="B837" s="2" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="C837" s="1">
         <v>0</v>
@@ -13947,7 +13947,7 @@
         <v>3669</v>
       </c>
       <c r="B838" s="2" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="C838" s="1">
         <v>0</v>
@@ -13959,7 +13959,7 @@
         <v>3670</v>
       </c>
       <c r="B839" s="2" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C839" s="1">
         <v>0</v>
@@ -13971,7 +13971,7 @@
         <v>3671</v>
       </c>
       <c r="B840" s="2" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="C840" s="1">
         <v>0</v>
@@ -13983,7 +13983,7 @@
         <v>3672</v>
       </c>
       <c r="B841" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C841" s="1">
         <v>0</v>
@@ -13995,7 +13995,7 @@
         <v>3673</v>
       </c>
       <c r="B842" s="2" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="C842" s="1">
         <v>0</v>
@@ -14007,7 +14007,7 @@
         <v>3674</v>
       </c>
       <c r="B843" s="2" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C843" s="1">
         <v>0</v>
@@ -14019,7 +14019,7 @@
         <v>3675</v>
       </c>
       <c r="B844" s="2" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="C844" s="1">
         <v>0</v>
@@ -14031,7 +14031,7 @@
         <v>3676</v>
       </c>
       <c r="B845" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C845" s="1">
         <v>0</v>
@@ -14043,7 +14043,7 @@
         <v>3677</v>
       </c>
       <c r="B846" s="2" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="C846" s="1">
         <v>0</v>
@@ -14055,7 +14055,7 @@
         <v>3678</v>
       </c>
       <c r="B847" s="2" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="C847" s="1">
         <v>0</v>
@@ -14067,7 +14067,7 @@
         <v>3679</v>
       </c>
       <c r="B848" s="2" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="C848" s="1">
         <v>0</v>
@@ -14079,7 +14079,7 @@
         <v>3687</v>
       </c>
       <c r="B849" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="C849" s="1">
         <v>0</v>
@@ -14091,7 +14091,7 @@
         <v>3688</v>
       </c>
       <c r="B850" s="2" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C850" s="1">
         <v>0</v>
@@ -14103,7 +14103,7 @@
         <v>3689</v>
       </c>
       <c r="B851" s="2" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="C851" s="1">
         <v>0</v>
@@ -14115,7 +14115,7 @@
         <v>3690</v>
       </c>
       <c r="B852" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="C852" s="1">
         <v>0</v>
@@ -14127,7 +14127,7 @@
         <v>3691</v>
       </c>
       <c r="B853" s="2" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C853" s="1">
         <v>0</v>
@@ -14139,7 +14139,7 @@
         <v>3692</v>
       </c>
       <c r="B854" s="2" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="C854" s="1">
         <v>0</v>
@@ -14151,7 +14151,7 @@
         <v>3693</v>
       </c>
       <c r="B855" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="C855" s="1">
         <v>0</v>
@@ -14163,7 +14163,7 @@
         <v>3695</v>
       </c>
       <c r="B856" s="2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="C856" s="1">
         <v>0</v>
@@ -14175,7 +14175,7 @@
         <v>3696</v>
       </c>
       <c r="B857" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="C857" s="1">
         <v>0</v>
@@ -14187,7 +14187,7 @@
         <v>3697</v>
       </c>
       <c r="B858" s="2" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="C858" s="1">
         <v>0</v>
@@ -14199,7 +14199,7 @@
         <v>3698</v>
       </c>
       <c r="B859" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="C859" s="1">
         <v>0</v>
@@ -14211,7 +14211,7 @@
         <v>3699</v>
       </c>
       <c r="B860" s="2" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="C860" s="1">
         <v>0</v>
@@ -14223,7 +14223,7 @@
         <v>3700</v>
       </c>
       <c r="B861" s="2" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="C861" s="1">
         <v>0</v>
@@ -14235,7 +14235,7 @@
         <v>3701</v>
       </c>
       <c r="B862" s="2" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="C862" s="1">
         <v>0</v>
@@ -14247,7 +14247,7 @@
         <v>3702</v>
       </c>
       <c r="B863" s="2" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="C863" s="1">
         <v>0</v>
@@ -14259,7 +14259,7 @@
         <v>3707</v>
       </c>
       <c r="B864" s="2" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="C864" s="1">
         <v>0</v>
@@ -14271,7 +14271,7 @@
         <v>3708</v>
       </c>
       <c r="B865" s="2" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="C865" s="1">
         <v>0</v>
@@ -14283,7 +14283,7 @@
         <v>3709</v>
       </c>
       <c r="B866" s="2" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="C866" s="1">
         <v>0</v>
@@ -14295,7 +14295,7 @@
         <v>3710</v>
       </c>
       <c r="B867" s="2" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="C867" s="1">
         <v>0</v>
@@ -14307,7 +14307,7 @@
         <v>3711</v>
       </c>
       <c r="B868" s="2" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C868" s="1">
         <v>0</v>
@@ -14319,7 +14319,7 @@
         <v>3712</v>
       </c>
       <c r="B869" s="2" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C869" s="1">
         <v>0</v>
@@ -14331,7 +14331,7 @@
         <v>3713</v>
       </c>
       <c r="B870" s="2" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C870" s="1">
         <v>0</v>
@@ -14343,7 +14343,7 @@
         <v>3714</v>
       </c>
       <c r="B871" s="2" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="C871" s="1">
         <v>0</v>
@@ -14355,7 +14355,7 @@
         <v>3715</v>
       </c>
       <c r="B872" s="2" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C872" s="1">
         <v>0</v>
@@ -14367,7 +14367,7 @@
         <v>3716</v>
       </c>
       <c r="B873" s="2" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C873" s="1">
         <v>0</v>
@@ -14379,7 +14379,7 @@
         <v>3717</v>
       </c>
       <c r="B874" s="2" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="C874" s="1">
         <v>0</v>
@@ -14391,7 +14391,7 @@
         <v>3718</v>
       </c>
       <c r="B875" s="2" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="C875" s="1">
         <v>0</v>
@@ -14403,7 +14403,7 @@
         <v>3719</v>
       </c>
       <c r="B876" s="2" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="C876" s="1">
         <v>0</v>
@@ -14415,7 +14415,7 @@
         <v>3720</v>
       </c>
       <c r="B877" s="2" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="C877" s="1">
         <v>0</v>
@@ -14427,7 +14427,7 @@
         <v>3727</v>
       </c>
       <c r="B878" s="2" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="C878" s="1">
         <v>0</v>
@@ -14439,7 +14439,7 @@
         <v>3728</v>
       </c>
       <c r="B879" s="2" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="C879" s="1">
         <v>0</v>
@@ -14451,7 +14451,7 @@
         <v>3729</v>
       </c>
       <c r="B880" s="2" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="C880" s="1">
         <v>0</v>
@@ -14463,7 +14463,7 @@
         <v>3730</v>
       </c>
       <c r="B881" s="2" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="C881" s="1">
         <v>0</v>
@@ -14475,7 +14475,7 @@
         <v>3731</v>
       </c>
       <c r="B882" s="2" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="C882" s="1">
         <v>0</v>
@@ -14487,7 +14487,7 @@
         <v>3732</v>
       </c>
       <c r="B883" s="2" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C883" s="1">
         <v>0</v>
@@ -14499,7 +14499,7 @@
         <v>3733</v>
       </c>
       <c r="B884" s="2" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="C884" s="1">
         <v>0</v>
@@ -14511,7 +14511,7 @@
         <v>3734</v>
       </c>
       <c r="B885" s="2" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="C885" s="1">
         <v>0</v>
@@ -14523,7 +14523,7 @@
         <v>3735</v>
       </c>
       <c r="B886" s="2" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="C886" s="1">
         <v>0</v>
@@ -14535,7 +14535,7 @@
         <v>3736</v>
       </c>
       <c r="B887" s="2" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="C887" s="1">
         <v>0</v>
@@ -14547,7 +14547,7 @@
         <v>3747</v>
       </c>
       <c r="B888" s="2" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="C888" s="1">
         <v>0</v>
@@ -14559,7 +14559,7 @@
         <v>3748</v>
       </c>
       <c r="B889" s="2" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="C889" s="1">
         <v>0</v>
@@ -14571,7 +14571,7 @@
         <v>3749</v>
       </c>
       <c r="B890" s="2" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="C890" s="1">
         <v>0</v>
@@ -14583,7 +14583,7 @@
         <v>3750</v>
       </c>
       <c r="B891" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C891" s="1">
         <v>0</v>
@@ -14595,7 +14595,7 @@
         <v>3767</v>
       </c>
       <c r="B892" s="2" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="C892" s="1">
         <v>0</v>
@@ -14607,7 +14607,7 @@
         <v>3787</v>
       </c>
       <c r="B893" s="2" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="C893" s="1">
         <v>0</v>
@@ -14619,7 +14619,7 @@
         <v>3807</v>
       </c>
       <c r="B894" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="C894" s="1">
         <v>0</v>
@@ -14631,7 +14631,7 @@
         <v>3827</v>
       </c>
       <c r="B895" s="2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="C895" s="1">
         <v>0</v>
@@ -14643,7 +14643,7 @@
         <v>3867</v>
       </c>
       <c r="B896" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="C896" s="1">
         <v>0</v>
@@ -14655,7 +14655,7 @@
         <v>3887</v>
       </c>
       <c r="B897" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="C897" s="1">
         <v>0</v>
@@ -14667,7 +14667,7 @@
         <v>3927</v>
       </c>
       <c r="B898" s="2" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="C898" s="1">
         <v>0</v>
@@ -14679,7 +14679,7 @@
         <v>3947</v>
       </c>
       <c r="B899" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C899" s="1">
         <v>0</v>
@@ -14691,7 +14691,7 @@
         <v>3967</v>
       </c>
       <c r="B900" s="2" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C900" s="1">
         <v>0</v>
@@ -14703,7 +14703,7 @@
         <v>4007</v>
       </c>
       <c r="B901" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C901" s="1">
         <v>0</v>
@@ -14715,7 +14715,7 @@
         <v>4047</v>
       </c>
       <c r="B902" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C902" s="1">
         <v>0</v>
@@ -14727,7 +14727,7 @@
         <v>4067</v>
       </c>
       <c r="B903" s="2" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C903" s="1">
         <v>0</v>
@@ -14739,7 +14739,7 @@
         <v>4087</v>
       </c>
       <c r="B904" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C904" s="1">
         <v>0</v>
@@ -14751,7 +14751,7 @@
         <v>4088</v>
       </c>
       <c r="B905" s="2" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C905" s="1">
         <v>0</v>
@@ -14763,7 +14763,7 @@
         <v>4127</v>
       </c>
       <c r="B906" s="2" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C906" s="1">
         <v>0</v>
@@ -14775,7 +14775,7 @@
         <v>4191</v>
       </c>
       <c r="B907" s="2" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="C907" s="1">
         <v>0</v>
@@ -14787,7 +14787,7 @@
         <v>4227</v>
       </c>
       <c r="B908" s="2" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C908" s="1">
         <v>0</v>
@@ -14799,7 +14799,7 @@
         <v>4228</v>
       </c>
       <c r="B909" s="2" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C909" s="1">
         <v>0</v>
@@ -14811,7 +14811,7 @@
         <v>4267</v>
       </c>
       <c r="B910" s="2" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C910" s="1">
         <v>0</v>
@@ -14823,7 +14823,7 @@
         <v>4287</v>
       </c>
       <c r="B911" s="2" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C911" s="1">
         <v>0</v>
@@ -14835,7 +14835,7 @@
         <v>4307</v>
       </c>
       <c r="B912" s="2" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="C912" s="1">
         <v>0</v>
@@ -14847,7 +14847,7 @@
         <v>4327</v>
       </c>
       <c r="B913" s="2" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="C913" s="1">
         <v>0</v>
@@ -14859,7 +14859,7 @@
         <v>4347</v>
       </c>
       <c r="B914" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C914" s="1">
         <v>0</v>
@@ -14871,7 +14871,7 @@
         <v>4367</v>
       </c>
       <c r="B915" s="2" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="C915" s="1">
         <v>0</v>
@@ -14883,7 +14883,7 @@
         <v>4387</v>
       </c>
       <c r="B916" s="2" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="C916" s="1">
         <v>0</v>
@@ -14895,7 +14895,7 @@
         <v>4407</v>
       </c>
       <c r="B917" s="2" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C917" s="1">
         <v>0</v>
@@ -14907,7 +14907,7 @@
         <v>4408</v>
       </c>
       <c r="B918" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="C918" s="1">
         <v>0</v>
@@ -14919,7 +14919,7 @@
         <v>4409</v>
       </c>
       <c r="B919" s="2" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="C919" s="1">
         <v>0</v>
@@ -14931,7 +14931,7 @@
         <v>4447</v>
       </c>
       <c r="B920" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C920" s="1">
         <v>0</v>
@@ -14943,7 +14943,7 @@
         <v>4467</v>
       </c>
       <c r="B921" s="2" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="C921" s="1">
         <v>0</v>
@@ -14955,7 +14955,7 @@
         <v>4490</v>
       </c>
       <c r="B922" s="2" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="C922" s="1">
         <v>0</v>
@@ -14967,7 +14967,7 @@
         <v>4507</v>
       </c>
       <c r="B923" s="2" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="C923" s="1">
         <v>0</v>
@@ -14979,7 +14979,7 @@
         <v>4527</v>
       </c>
       <c r="B924" s="2" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="C924" s="1">
         <v>0</v>
@@ -14991,7 +14991,7 @@
         <v>4547</v>
       </c>
       <c r="B925" s="2" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="C925" s="1">
         <v>0</v>
@@ -15003,7 +15003,7 @@
         <v>4587</v>
       </c>
       <c r="B926" s="2" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="C926" s="1">
         <v>0</v>
@@ -15015,7 +15015,7 @@
         <v>4627</v>
       </c>
       <c r="B927" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C927" s="1">
         <v>0</v>
@@ -15027,7 +15027,7 @@
         <v>4667</v>
       </c>
       <c r="B928" s="2" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="C928" s="1">
         <v>0</v>
@@ -15039,7 +15039,7 @@
         <v>4687</v>
       </c>
       <c r="B929" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C929" s="1">
         <v>0</v>
@@ -15051,7 +15051,7 @@
         <v>4707</v>
       </c>
       <c r="B930" s="2" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="C930" s="1">
         <v>0</v>
@@ -15063,7 +15063,7 @@
         <v>4727</v>
       </c>
       <c r="B931" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="C931" s="1">
         <v>0</v>
@@ -15075,7 +15075,7 @@
         <v>4747</v>
       </c>
       <c r="B932" s="2" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="C932" s="1">
         <v>0</v>
@@ -15087,7 +15087,7 @@
         <v>4767</v>
       </c>
       <c r="B933" s="2" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="C933" s="1">
         <v>0</v>
@@ -15099,7 +15099,7 @@
         <v>4768</v>
       </c>
       <c r="B934" s="2" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="C934" s="1">
         <v>0</v>
@@ -15111,7 +15111,7 @@
         <v>4769</v>
       </c>
       <c r="B935" s="2" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="C935" s="1">
         <v>0</v>
@@ -15123,7 +15123,7 @@
         <v>4770</v>
       </c>
       <c r="B936" s="2" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="C936" s="1">
         <v>0</v>
@@ -15135,7 +15135,7 @@
         <v>4771</v>
       </c>
       <c r="B937" s="2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C937" s="1">
         <v>0</v>
@@ -15147,7 +15147,7 @@
         <v>4772</v>
       </c>
       <c r="B938" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="C938" s="1">
         <v>0</v>
@@ -15159,7 +15159,7 @@
         <v>4773</v>
       </c>
       <c r="B939" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="C939" s="1">
         <v>0</v>
@@ -15171,7 +15171,7 @@
         <v>4774</v>
       </c>
       <c r="B940" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="C940" s="1">
         <v>0</v>
@@ -15183,7 +15183,7 @@
         <v>4775</v>
       </c>
       <c r="B941" s="2" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="C941" s="1">
         <v>0</v>
@@ -15195,7 +15195,7 @@
         <v>4776</v>
       </c>
       <c r="B942" s="2" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="C942" s="1">
         <v>0</v>
@@ -15207,7 +15207,7 @@
         <v>4777</v>
       </c>
       <c r="B943" s="2" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="C943" s="1">
         <v>0</v>
@@ -15219,7 +15219,7 @@
         <v>4778</v>
       </c>
       <c r="B944" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C944" s="1">
         <v>0</v>
@@ -15231,7 +15231,7 @@
         <v>4779</v>
       </c>
       <c r="B945" s="2" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="C945" s="1">
         <v>0</v>
@@ -15243,7 +15243,7 @@
         <v>4780</v>
       </c>
       <c r="B946" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C946" s="1">
         <v>0</v>
@@ -15255,7 +15255,7 @@
         <v>4781</v>
       </c>
       <c r="B947" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C947" s="1">
         <v>0</v>
@@ -15267,7 +15267,7 @@
         <v>4782</v>
       </c>
       <c r="B948" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="C948" s="1">
         <v>0</v>
@@ -15279,7 +15279,7 @@
         <v>4783</v>
       </c>
       <c r="B949" s="2" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C949" s="1">
         <v>0</v>
@@ -15291,7 +15291,7 @@
         <v>4784</v>
       </c>
       <c r="B950" s="2" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C950" s="1">
         <v>0</v>
@@ -15303,7 +15303,7 @@
         <v>4785</v>
       </c>
       <c r="B951" s="2" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="C951" s="1">
         <v>0</v>
@@ -15315,7 +15315,7 @@
         <v>4786</v>
       </c>
       <c r="B952" s="2" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="C952" s="1">
         <v>0</v>
@@ -15327,7 +15327,7 @@
         <v>4787</v>
       </c>
       <c r="B953" s="2" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="C953" s="1">
         <v>0</v>
@@ -15339,7 +15339,7 @@
         <v>4788</v>
       </c>
       <c r="B954" s="2" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C954" s="1">
         <v>0</v>
@@ -15351,7 +15351,7 @@
         <v>4789</v>
       </c>
       <c r="B955" s="2" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="C955" s="1">
         <v>0</v>
@@ -15363,7 +15363,7 @@
         <v>4790</v>
       </c>
       <c r="B956" s="2" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="C956" s="1">
         <v>0</v>
@@ -15375,7 +15375,7 @@
         <v>4807</v>
       </c>
       <c r="B957" s="2" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="C957" s="1">
         <v>0</v>
@@ -15387,7 +15387,7 @@
         <v>4808</v>
       </c>
       <c r="B958" s="2" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C958" s="1">
         <v>0</v>
@@ -15399,7 +15399,7 @@
         <v>4809</v>
       </c>
       <c r="B959" s="2" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="C959" s="1">
         <v>0</v>
@@ -15411,7 +15411,7 @@
         <v>4810</v>
       </c>
       <c r="B960" s="2" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="C960" s="1">
         <v>0</v>
@@ -15423,7 +15423,7 @@
         <v>4811</v>
       </c>
       <c r="B961" s="2" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="C961" s="1">
         <v>0</v>
@@ -15435,7 +15435,7 @@
         <v>4812</v>
       </c>
       <c r="B962" s="2" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="C962" s="1">
         <v>0</v>
@@ -15447,7 +15447,7 @@
         <v>4813</v>
       </c>
       <c r="B963" s="2" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="C963" s="1">
         <v>0</v>
@@ -15459,7 +15459,7 @@
         <v>4814</v>
       </c>
       <c r="B964" s="2" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="C964" s="1">
         <v>0</v>
@@ -15471,7 +15471,7 @@
         <v>4815</v>
       </c>
       <c r="B965" s="2" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C965" s="1">
         <v>0</v>
@@ -15483,7 +15483,7 @@
         <v>4827</v>
       </c>
       <c r="B966" s="2" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C966" s="1">
         <v>0</v>
@@ -15495,7 +15495,7 @@
         <v>4828</v>
       </c>
       <c r="B967" s="2" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C967" s="1">
         <v>0</v>
@@ -15507,7 +15507,7 @@
         <v>4829</v>
       </c>
       <c r="B968" s="2" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C968" s="1">
         <v>0</v>
@@ -15519,7 +15519,7 @@
         <v>4847</v>
       </c>
       <c r="B969" s="2" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C969" s="1">
         <v>0</v>
@@ -15531,7 +15531,7 @@
         <v>4867</v>
       </c>
       <c r="B970" s="2" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="C970" s="1">
         <v>0</v>
@@ -15543,7 +15543,7 @@
         <v>4887</v>
       </c>
       <c r="B971" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="C971" s="1">
         <v>0</v>
@@ -15555,7 +15555,7 @@
         <v>4927</v>
       </c>
       <c r="B972" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C972" s="1">
         <v>0</v>
@@ -15567,7 +15567,7 @@
         <v>4947</v>
       </c>
       <c r="B973" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="C973" s="1">
         <v>0</v>
@@ -15579,7 +15579,7 @@
         <v>4970</v>
       </c>
       <c r="B974" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="C974" s="1">
         <v>0</v>
@@ -15591,7 +15591,7 @@
         <v>5007</v>
       </c>
       <c r="B975" s="2" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="C975" s="1">
         <v>0</v>

--- a/data/entrada/inventario/servicios.xlsx
+++ b/data/entrada/inventario/servicios.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amarzal/_Activo/eco/CoAna/data/entrada/inventario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B3A272-A5C1-A444-9579-7FB75EA43C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F05AA17E-96D2-1D4C-BA73-62D765FE61F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="660" windowWidth="34320" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1239" uniqueCount="1187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1239" uniqueCount="1186">
   <si>
     <t>servicio</t>
   </si>
@@ -3578,9 +3578,6 @@
   </si>
   <si>
     <t>udpea</t>
-  </si>
-  <si>
-    <t>dag-uiic</t>
   </si>
 </sst>
 </file>
@@ -16480,7 +16477,7 @@
         <v>181</v>
       </c>
       <c r="E925" s="2" t="s">
-        <v>1186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="926" spans="1:5" x14ac:dyDescent="0.2">
